--- a/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_47.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_47.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4153872.014066651</v>
+        <v>4154845.825898908</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13581283.20397973</v>
+        <v>13590227.91789529</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13581283.20397973</v>
+        <v>13590227.91789529</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>561.066057021721</v>
+        <v>6622.248428704141</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>561.066057021721</v>
+        <v>6622.248428704141</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20691179.40653732</v>
+        <v>20689180.7116271</v>
       </c>
     </row>
   </sheetData>
@@ -669,13 +669,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I2" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.50414770182039</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -742,19 +742,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>174.0029632184479</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S3" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>177.325618254799</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,10 +906,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>5.608919435675552</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.50414770182039</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -970,64 +970,64 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>361.0999124455193</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>342.6720972219126</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>110.5396437552028</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>133.5184388018132</v>
+      </c>
+      <c r="S6" t="n">
+        <v>62.44885845517734</v>
+      </c>
+      <c r="T6" t="n">
         <v>374</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>347.9376868977026</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>209.5726123064429</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>374</v>
-      </c>
-      <c r="S6" t="n">
-        <v>71.31115105324892</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4.473444462796863</v>
-      </c>
       <c r="U6" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O7" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>87.36594612241093</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T8" t="n">
         <v>184.8629887637397</v>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>330.0103162242497</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>65.27280584929355</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
-        <v>133.5184388018132</v>
+        <v>374</v>
       </c>
       <c r="S9" t="n">
         <v>62.44885845517734</v>
@@ -1264,10 +1264,10 @@
         <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1957842884886531</v>
+        <v>374</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>374</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
@@ -1380,13 +1380,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.36239741264433</v>
+        <v>81.36641751314687</v>
       </c>
       <c r="H11" t="n">
-        <v>72.7233722713666</v>
+        <v>69.65376767688156</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9247431442083656</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1416,13 +1416,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>142.0601778525742</v>
+        <v>142.1517858927751</v>
       </c>
       <c r="T11" t="n">
-        <v>259.5690792160011</v>
+        <v>259.5866772059508</v>
       </c>
       <c r="U11" t="n">
-        <v>328.109698558661</v>
+        <v>328.1100201667011</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1447,7 +1447,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>40.09991244551929</v>
+        <v>220.0700289256061</v>
       </c>
       <c r="D12" t="n">
         <v>26.93768689770263</v>
@@ -1459,10 +1459,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>3.993158516536766</v>
+        <v>3.995309459933026</v>
       </c>
       <c r="H12" t="n">
-        <v>187.1189200033005</v>
+        <v>3.980426809062635</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1492,22 +1492,22 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>500.932929367851</v>
+        <v>180.0664765376623</v>
       </c>
       <c r="S12" t="n">
-        <v>131.7003678891396</v>
+        <v>131.7403207193283</v>
       </c>
       <c r="T12" t="n">
-        <v>81.34934068921194</v>
+        <v>81.35801050053266</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16125598660182</v>
+        <v>79.16139749603582</v>
       </c>
       <c r="V12" t="n">
         <v>414.5106671915202</v>
       </c>
       <c r="W12" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X12" t="n">
         <v>419.8627394453875</v>
@@ -1553,28 +1553,28 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9.517497010238174</v>
+        <v>9.78559537089393</v>
       </c>
       <c r="M13" t="n">
-        <v>101.5443818943532</v>
+        <v>101.8270540255007</v>
       </c>
       <c r="N13" t="n">
-        <v>154.4301408454554</v>
+        <v>154.7060916651275</v>
       </c>
       <c r="O13" t="n">
-        <v>231.000383751146</v>
+        <v>231.2552689970478</v>
       </c>
       <c r="P13" t="n">
-        <v>290.7677661807365</v>
+        <v>290.9858645413923</v>
       </c>
       <c r="Q13" t="n">
-        <v>352.4422664255979</v>
+        <v>352.593266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.4666853582003</v>
+        <v>377.5477673254134</v>
       </c>
       <c r="S13" t="n">
-        <v>30.46857806351119</v>
+        <v>30.5000042930194</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9247431442083234</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>142.0601778525742</v>
+        <v>139.1041209967824</v>
       </c>
       <c r="T14" t="n">
         <v>259.5690792160011</v>
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
         <v>223.2591792246629</v>
       </c>
       <c r="D15" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
         <v>3.993158516536777</v>
@@ -1747,10 +1747,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1854,13 +1854,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>81.36239741264436</v>
+        <v>78.4063405568529</v>
       </c>
       <c r="H17" t="n">
         <v>72.72337227136661</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9247431442085484</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>223.2591792246629</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
         <v>3.993158516536777</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>179.932929367851</v>
+        <v>363.0921961469944</v>
       </c>
       <c r="S18" t="n">
         <v>131.7003678891396</v>
@@ -1975,13 +1975,13 @@
         <v>81.34934068921193</v>
       </c>
       <c r="U18" t="n">
-        <v>79.16125598660184</v>
+        <v>400.1612559866018</v>
       </c>
       <c r="V18" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W18" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X18" t="n">
         <v>98.86273944538755</v>
@@ -2091,13 +2091,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>81.36239741264433</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H20" t="n">
-        <v>72.7233722713666</v>
+        <v>72.72337227136661</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9247431442083656</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2127,13 +2127,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>142.0601778525742</v>
+        <v>139.1041209967824</v>
       </c>
       <c r="T20" t="n">
         <v>259.5690792160011</v>
       </c>
       <c r="U20" t="n">
-        <v>328.109698558661</v>
+        <v>328.1096985586609</v>
       </c>
       <c r="V20" t="n">
         <v>308.8510241668239</v>
@@ -2158,22 +2158,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>223.2591792246629</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>3.993158516536766</v>
+        <v>187.1524252956803</v>
       </c>
       <c r="H21" t="n">
-        <v>3.959653224156966</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2209,16 +2209,16 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T21" t="n">
-        <v>81.34934068921194</v>
+        <v>81.34934068921193</v>
       </c>
       <c r="U21" t="n">
-        <v>79.16125598660182</v>
+        <v>400.1612559866018</v>
       </c>
       <c r="V21" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W21" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X21" t="n">
         <v>98.86273944538755</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>9.517497010238174</v>
+        <v>9.517497010238188</v>
       </c>
       <c r="M22" t="n">
         <v>101.5443818943532</v>
@@ -2273,19 +2273,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O22" t="n">
-        <v>231.000383751146</v>
+        <v>231.0003837511461</v>
       </c>
       <c r="P22" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q22" t="n">
-        <v>352.4422664255979</v>
+        <v>352.442266425598</v>
       </c>
       <c r="R22" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S22" t="n">
-        <v>30.46857806351119</v>
+        <v>30.46857806351117</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,13 +2328,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>81.36239741264433</v>
+        <v>78.40634055685268</v>
       </c>
       <c r="H23" t="n">
         <v>72.7233722713666</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9247431442083656</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2395,10 +2395,10 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>223.2591792246629</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
@@ -2440,10 +2440,10 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>179.932929367851</v>
+        <v>500.932929367851</v>
       </c>
       <c r="S24" t="n">
-        <v>131.7003678891396</v>
+        <v>314.8596346682835</v>
       </c>
       <c r="T24" t="n">
         <v>81.34934068921194</v>
@@ -2565,10 +2565,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.36239741264433</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H26" t="n">
-        <v>77.52891541557497</v>
+        <v>77.52891541557517</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U26" t="n">
-        <v>328.109698558661</v>
+        <v>328.1096985586609</v>
       </c>
       <c r="V26" t="n">
         <v>308.8510241668239</v>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>384.5565566463266</v>
+        <v>246.7158234254701</v>
       </c>
       <c r="C27" t="n">
-        <v>223.2591792246628</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D27" t="n">
         <v>26.93768689770263</v>
@@ -2644,10 +2644,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>3.993158516536766</v>
+        <v>3.993158516536777</v>
       </c>
       <c r="H27" t="n">
-        <v>3.959653224156966</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2683,22 +2683,22 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T27" t="n">
-        <v>81.34934068921194</v>
+        <v>81.34934068921193</v>
       </c>
       <c r="U27" t="n">
-        <v>400.1612559866018</v>
+        <v>79.16125598660184</v>
       </c>
       <c r="V27" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W27" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.517497010238174</v>
+        <v>9.517497010238188</v>
       </c>
       <c r="M28" t="n">
         <v>101.5443818943532</v>
@@ -2747,19 +2747,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O28" t="n">
-        <v>231.000383751146</v>
+        <v>231.0003837511461</v>
       </c>
       <c r="P28" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q28" t="n">
-        <v>352.4422664255979</v>
+        <v>352.442266425598</v>
       </c>
       <c r="R28" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S28" t="n">
-        <v>30.46857806351119</v>
+        <v>30.46857806351117</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>160.9993129555745</v>
+        <v>165.8048560997829</v>
       </c>
       <c r="C29" t="n">
         <v>128.4745782429939</v>
@@ -2805,7 +2805,7 @@
         <v>81.36239741264433</v>
       </c>
       <c r="H29" t="n">
-        <v>77.52891541557497</v>
+        <v>72.7233722713666</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E30" t="n">
         <v>21.67209722191262</v>
@@ -2926,16 +2926,16 @@
         <v>79.16125598660182</v>
       </c>
       <c r="V30" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>261.5506595452777</v>
+        <v>261.5506595452778</v>
       </c>
     </row>
     <row r="31">
@@ -3039,13 +3039,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.36239741264436</v>
+        <v>81.36239741264433</v>
       </c>
       <c r="H32" t="n">
-        <v>72.72337227136661</v>
+        <v>72.7233722713666</v>
       </c>
       <c r="I32" t="n">
-        <v>4.80554314420855</v>
+        <v>4.805543144208367</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U32" t="n">
-        <v>328.1096985586609</v>
+        <v>328.109698558661</v>
       </c>
       <c r="V32" t="n">
         <v>308.8510241668239</v>
@@ -3103,25 +3103,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>3.993158516536777</v>
+        <v>3.993158516536766</v>
       </c>
       <c r="H33" t="n">
-        <v>3.95965322415698</v>
+        <v>3.959653224156966</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3157,22 +3157,22 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T33" t="n">
-        <v>81.34934068921193</v>
+        <v>81.34934068921194</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16125598660184</v>
+        <v>79.16125598660182</v>
       </c>
       <c r="V33" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>294.532409688972</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y33" t="n">
-        <v>399.3913927661343</v>
+        <v>261.5506595452777</v>
       </c>
     </row>
     <row r="34">
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>9.517497010238188</v>
+        <v>9.517497010238174</v>
       </c>
       <c r="M34" t="n">
         <v>101.5443818943532</v>
@@ -3221,19 +3221,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O34" t="n">
-        <v>231.0003837511461</v>
+        <v>231.000383751146</v>
       </c>
       <c r="P34" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q34" t="n">
-        <v>352.442266425598</v>
+        <v>352.4422664255979</v>
       </c>
       <c r="R34" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S34" t="n">
-        <v>30.46857806351117</v>
+        <v>30.46857806351119</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3312,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>118.0601778525742</v>
+        <v>113.4745209967827</v>
       </c>
       <c r="T35" t="n">
         <v>235.5690792160011</v>
       </c>
       <c r="U35" t="n">
-        <v>303.4048417030991</v>
+        <v>304.1096985586609</v>
       </c>
       <c r="V35" t="n">
         <v>284.8510241668239</v>
@@ -3343,10 +3343,10 @@
         <v>39.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>16.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>2.937686897702633</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
@@ -3358,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>86.11207851983723</v>
+        <v>83.94446820502327</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3388,13 +3388,13 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>500.932929367851</v>
+        <v>155.932929367851</v>
       </c>
       <c r="S36" t="n">
         <v>107.7003678891396</v>
       </c>
       <c r="T36" t="n">
-        <v>402.3493406892119</v>
+        <v>57.34934068921193</v>
       </c>
       <c r="U36" t="n">
         <v>55.16125598660184</v>
@@ -3516,7 +3516,7 @@
         <v>57.36239741264433</v>
       </c>
       <c r="H38" t="n">
-        <v>48.01851541583258</v>
+        <v>48.7233722713666</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>-9.135548300149619e-11</v>
       </c>
       <c r="S38" t="n">
         <v>118.0601778525742</v>
@@ -3561,7 +3561,7 @@
         <v>284.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>293.3734759809475</v>
+        <v>288.7878191252498</v>
       </c>
       <c r="X38" t="n">
         <v>247.2818334606677</v>
@@ -3580,16 +3580,16 @@
         <v>39.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>16.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>2.937686897702633</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3625,19 +3625,19 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>500.932929367851</v>
+        <v>239.877397572932</v>
       </c>
       <c r="S39" t="n">
         <v>107.7003678891396</v>
       </c>
       <c r="T39" t="n">
-        <v>135.7697587688385</v>
+        <v>57.34934068921194</v>
       </c>
       <c r="U39" t="n">
         <v>55.16125598660182</v>
       </c>
       <c r="V39" t="n">
-        <v>414.5106671915202</v>
+        <v>69.51066719152016</v>
       </c>
       <c r="W39" t="n">
         <v>432.3731429098285</v>
@@ -3750,10 +3750,10 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>57.36239741264435</v>
+        <v>52.77674055685252</v>
       </c>
       <c r="H41" t="n">
-        <v>48.01851541580464</v>
+        <v>48.7233722713666</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
         <v>235.5690792160011</v>
       </c>
       <c r="U41" t="n">
-        <v>304.1096985586609</v>
+        <v>304.109698558661</v>
       </c>
       <c r="V41" t="n">
         <v>284.8510241668239</v>
@@ -3814,25 +3814,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>39.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C42" t="n">
-        <v>16.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>2.937686897702633</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>78.42041807962671</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>81.6165654270511</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3862,16 +3862,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>500.932929367851</v>
+        <v>155.932929367851</v>
       </c>
       <c r="S42" t="n">
         <v>107.7003678891396</v>
       </c>
       <c r="T42" t="n">
-        <v>402.3493406892119</v>
+        <v>57.34934068921194</v>
       </c>
       <c r="U42" t="n">
-        <v>400.1612559866018</v>
+        <v>55.16125598660182</v>
       </c>
       <c r="V42" t="n">
         <v>69.51066719152016</v>
@@ -3883,7 +3883,7 @@
         <v>74.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>399.3913927661343</v>
+        <v>54.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -3926,25 +3926,25 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>77.54438189435318</v>
+        <v>77.54438189435319</v>
       </c>
       <c r="N43" t="n">
         <v>130.4301408454554</v>
       </c>
       <c r="O43" t="n">
-        <v>207.0003837511461</v>
+        <v>207.000383751146</v>
       </c>
       <c r="P43" t="n">
         <v>266.7677661807365</v>
       </c>
       <c r="Q43" t="n">
-        <v>328.442266425598</v>
+        <v>328.4422664255979</v>
       </c>
       <c r="R43" t="n">
         <v>353.4666853582003</v>
       </c>
       <c r="S43" t="n">
-        <v>6.468578063511176</v>
+        <v>6.468578063511188</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,10 +3987,10 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>57.36239741264433</v>
+        <v>52.7767405568525</v>
       </c>
       <c r="H44" t="n">
-        <v>48.01851541580466</v>
+        <v>48.72337227136661</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
         <v>235.5690792160011</v>
       </c>
       <c r="U44" t="n">
-        <v>304.109698558661</v>
+        <v>304.1096985586609</v>
       </c>
       <c r="V44" t="n">
         <v>284.8510241668239</v>
@@ -4051,25 +4051,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>117.976974725953</v>
+        <v>39.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>16.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>2.937686897702633</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4102,16 +4102,16 @@
         <v>155.932929367851</v>
       </c>
       <c r="S45" t="n">
-        <v>452.7003678891396</v>
+        <v>107.7003678891396</v>
       </c>
       <c r="T45" t="n">
-        <v>57.34934068921194</v>
+        <v>179.0130943754176</v>
       </c>
       <c r="U45" t="n">
-        <v>400.1612559866018</v>
+        <v>55.16125598660184</v>
       </c>
       <c r="V45" t="n">
-        <v>414.5106671915202</v>
+        <v>69.51066719152016</v>
       </c>
       <c r="W45" t="n">
         <v>87.37314290982852</v>
@@ -4163,25 +4163,25 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>77.54438189435319</v>
+        <v>77.54438189435318</v>
       </c>
       <c r="N46" t="n">
         <v>130.4301408454554</v>
       </c>
       <c r="O46" t="n">
-        <v>207.000383751146</v>
+        <v>207.0003837511461</v>
       </c>
       <c r="P46" t="n">
         <v>266.7677661807365</v>
       </c>
       <c r="Q46" t="n">
-        <v>328.4422664255979</v>
+        <v>328.442266425598</v>
       </c>
       <c r="R46" t="n">
         <v>353.4666853582003</v>
       </c>
       <c r="S46" t="n">
-        <v>6.468578063511188</v>
+        <v>6.468578063511176</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,49 +4297,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.731003807232</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C2" t="n">
-        <v>58.7566823496624</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D2" t="n">
-        <v>48.31309069324847</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E2" t="n">
-        <v>43.90572745398721</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F2" t="n">
-        <v>38.96670855700554</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G2" t="n">
-        <v>35.58557518755106</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H2" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I2" t="n">
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K2" t="n">
-        <v>81.5583303517588</v>
+        <v>400.2796902997726</v>
       </c>
       <c r="L2" t="n">
-        <v>327.128108133742</v>
+        <v>770.5396902997726</v>
       </c>
       <c r="M2" t="n">
-        <v>697.388108133742</v>
+        <v>770.5396902997726</v>
       </c>
       <c r="N2" t="n">
-        <v>1067.648108133742</v>
+        <v>1140.799690299772</v>
       </c>
       <c r="O2" t="n">
-        <v>1067.648108133742</v>
+        <v>1140.799690299772</v>
       </c>
       <c r="P2" t="n">
-        <v>1125.74</v>
+        <v>1199.463896688644</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4348,25 +4348,25 @@
         <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T2" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U2" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V2" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W2" t="n">
-        <v>498.2245180486953</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X2" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.5585926512467</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1051.142534488436</v>
+        <v>1079.663263689516</v>
       </c>
       <c r="C3" t="n">
-        <v>1051.142534488436</v>
+        <v>1079.663263689516</v>
       </c>
       <c r="D3" t="n">
-        <v>1051.142534488436</v>
+        <v>1079.663263689516</v>
       </c>
       <c r="E3" t="n">
-        <v>705.0091029511505</v>
+        <v>1079.663263689516</v>
       </c>
       <c r="F3" t="n">
-        <v>361.9421914987495</v>
+        <v>903.9026947819933</v>
       </c>
       <c r="G3" t="n">
-        <v>33.13396963146437</v>
+        <v>575.0966455848054</v>
       </c>
       <c r="H3" t="n">
-        <v>33.13396963146437</v>
+        <v>241.7346173614335</v>
       </c>
       <c r="I3" t="n">
-        <v>33.13396963146437</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="J3" t="n">
-        <v>177.6113405614803</v>
+        <v>174.7984703728012</v>
       </c>
       <c r="K3" t="n">
-        <v>401.8775591086939</v>
+        <v>399.4085458068072</v>
       </c>
       <c r="L3" t="n">
-        <v>720.3885386284223</v>
+        <v>718.3818833454036</v>
       </c>
       <c r="M3" t="n">
-        <v>861.5031803712816</v>
+        <v>860.0360750882628</v>
       </c>
       <c r="N3" t="n">
-        <v>1051.274153846774</v>
+        <v>1050.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.994549492757</v>
+        <v>1341.587921002191</v>
       </c>
       <c r="P3" t="n">
         <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1496</v>
+        <v>1349.738421006376</v>
       </c>
       <c r="R3" t="n">
-        <v>1360.997993968056</v>
+        <v>1214.871311105555</v>
       </c>
       <c r="S3" t="n">
-        <v>1297.877982568697</v>
+        <v>1151.791656100326</v>
       </c>
       <c r="T3" t="n">
-        <v>1118.761196452738</v>
+        <v>1147.281782714996</v>
       </c>
       <c r="U3" t="n">
-        <v>1118.563291606351</v>
+        <v>1147.084020807432</v>
       </c>
       <c r="V3" t="n">
-        <v>1103.906052018957</v>
+        <v>1132.426781220038</v>
       </c>
       <c r="W3" t="n">
-        <v>1071.205907665595</v>
+        <v>1099.726636866676</v>
       </c>
       <c r="X3" t="n">
-        <v>1051.142534488436</v>
+        <v>1079.663263689516</v>
       </c>
       <c r="Y3" t="n">
-        <v>1051.142534488436</v>
+        <v>1079.663263689516</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>259.1973975316665</v>
+        <v>404.1174293695179</v>
       </c>
       <c r="C4" t="n">
-        <v>259.1973975316665</v>
+        <v>530.1194351879536</v>
       </c>
       <c r="D4" t="n">
-        <v>314.2884424888549</v>
+        <v>643.4385793129537</v>
       </c>
       <c r="E4" t="n">
-        <v>432.1173467002679</v>
+        <v>761.2674835243668</v>
       </c>
       <c r="F4" t="n">
-        <v>556.4783192922034</v>
+        <v>885.6284561163022</v>
       </c>
       <c r="G4" t="n">
-        <v>710.066980261056</v>
+        <v>1039.218902331056</v>
       </c>
       <c r="H4" t="n">
-        <v>881.2025562401257</v>
+        <v>1210.370350769143</v>
       </c>
       <c r="I4" t="n">
-        <v>881.2025562401257</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.462556240126</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.983127881912</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L4" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R4" t="n">
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T4" t="n">
-        <v>259.1973975316665</v>
+        <v>29.92</v>
       </c>
       <c r="U4" t="n">
-        <v>259.1973975316665</v>
+        <v>29.92</v>
       </c>
       <c r="V4" t="n">
-        <v>259.1973975316665</v>
+        <v>29.92</v>
       </c>
       <c r="W4" t="n">
-        <v>259.1973975316665</v>
+        <v>29.92</v>
       </c>
       <c r="X4" t="n">
-        <v>259.1973975316665</v>
+        <v>180.9507910241935</v>
       </c>
       <c r="Y4" t="n">
-        <v>259.1973975316665</v>
+        <v>292.3600917032257</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.731003807232</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C5" t="n">
-        <v>58.7566823496624</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D5" t="n">
-        <v>48.31309069324847</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E5" t="n">
-        <v>43.90572745398721</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F5" t="n">
-        <v>38.96670855700554</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G5" t="n">
-        <v>35.58557518755106</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H5" t="n">
         <v>29.92</v>
@@ -4558,22 +4558,22 @@
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>400.18</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>770.4399999999999</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="M5" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N5" t="n">
-        <v>1437.908108133742</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="O5" t="n">
-        <v>1437.908108133742</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="P5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U5" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V5" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W5" t="n">
-        <v>498.2245180486953</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X5" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.5585926512467</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>593.0617163678237</v>
+        <v>852.457023659227</v>
       </c>
       <c r="C6" t="n">
-        <v>593.0617163678237</v>
+        <v>487.7096373506217</v>
       </c>
       <c r="D6" t="n">
-        <v>241.6095073802453</v>
+        <v>487.7096373506217</v>
       </c>
       <c r="E6" t="n">
-        <v>241.6095073802453</v>
+        <v>141.5762058133362</v>
       </c>
       <c r="F6" t="n">
-        <v>241.6095073802453</v>
+        <v>141.5762058133362</v>
       </c>
       <c r="G6" t="n">
-        <v>241.6095073802453</v>
+        <v>29.92</v>
       </c>
       <c r="H6" t="n">
-        <v>241.6095073802453</v>
+        <v>29.92</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K6" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L6" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M6" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N6" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1115.008252590758</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S6" t="n">
-        <v>1042.976786880405</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T6" t="n">
-        <v>1038.458156109903</v>
+        <v>920.0755426847068</v>
       </c>
       <c r="U6" t="n">
-        <v>1038.260251263517</v>
+        <v>919.8777807771424</v>
       </c>
       <c r="V6" t="n">
-        <v>1023.603011676123</v>
+        <v>905.2205411897484</v>
       </c>
       <c r="W6" t="n">
-        <v>990.9028673227607</v>
+        <v>872.5203968363862</v>
       </c>
       <c r="X6" t="n">
-        <v>970.8394941456015</v>
+        <v>852.457023659227</v>
       </c>
       <c r="Y6" t="n">
-        <v>970.8394941456015</v>
+        <v>852.457023659227</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>654.5935815663379</v>
+        <v>216.7976894066533</v>
       </c>
       <c r="C7" t="n">
-        <v>654.5935815663379</v>
+        <v>342.7996952250891</v>
       </c>
       <c r="D7" t="n">
-        <v>654.5935815663379</v>
+        <v>456.1188393500892</v>
       </c>
       <c r="E7" t="n">
-        <v>654.5935815663379</v>
+        <v>573.9477435615022</v>
       </c>
       <c r="F7" t="n">
-        <v>654.5935815663379</v>
+        <v>698.3087161534377</v>
       </c>
       <c r="G7" t="n">
-        <v>654.5935815663379</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="H7" t="n">
-        <v>654.5935815663379</v>
+        <v>1023.050610806278</v>
       </c>
       <c r="I7" t="n">
-        <v>881.2025562401257</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="J7" t="n">
-        <v>1251.462556240126</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K7" t="n">
-        <v>1382.983127881912</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M7" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N7" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O7" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P7" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.34367574991084</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T7" t="n">
-        <v>259.1973975316665</v>
+        <v>216.7976894066533</v>
       </c>
       <c r="U7" t="n">
-        <v>505.7585226289696</v>
+        <v>216.7976894066533</v>
       </c>
       <c r="V7" t="n">
-        <v>654.5935815663379</v>
+        <v>216.7976894066533</v>
       </c>
       <c r="W7" t="n">
-        <v>654.5935815663379</v>
+        <v>216.7976894066533</v>
       </c>
       <c r="X7" t="n">
-        <v>654.5935815663379</v>
+        <v>216.7976894066533</v>
       </c>
       <c r="Y7" t="n">
-        <v>654.5935815663379</v>
+        <v>216.7976894066533</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106.8684999460195</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C8" t="n">
-        <v>56.89417848844992</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D8" t="n">
-        <v>46.450586832036</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E8" t="n">
-        <v>42.04322359277474</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F8" t="n">
-        <v>37.10420469579307</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G8" t="n">
-        <v>33.72713203391686</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H8" t="n">
-        <v>29.92</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1407.751569573322</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T8" t="n">
-        <v>1221.021277892777</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U8" t="n">
-        <v>969.3160547407873</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V8" t="n">
-        <v>737.1433030571268</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W8" t="n">
-        <v>496.3620141874828</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X8" t="n">
-        <v>302.1379399847881</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y8" t="n">
-        <v>189.6960887900342</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="9">
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>746.1195952961839</v>
+        <v>95.85212712049854</v>
       </c>
       <c r="C9" t="n">
-        <v>381.3722089875785</v>
+        <v>95.85212712049854</v>
       </c>
       <c r="D9" t="n">
-        <v>29.92</v>
+        <v>95.85212712049854</v>
       </c>
       <c r="E9" t="n">
         <v>29.92</v>
@@ -4898,28 +4898,28 @@
         <v>1349.538506374912</v>
       </c>
       <c r="R9" t="n">
-        <v>1214.671396474091</v>
+        <v>971.7607285971344</v>
       </c>
       <c r="S9" t="n">
-        <v>1151.591741468861</v>
+        <v>908.6810735919048</v>
       </c>
       <c r="T9" t="n">
-        <v>1147.081868083532</v>
+        <v>904.1712002065755</v>
       </c>
       <c r="U9" t="n">
-        <v>1146.884106175968</v>
+        <v>526.3934224287976</v>
       </c>
       <c r="V9" t="n">
-        <v>1132.226866588574</v>
+        <v>148.6156446510198</v>
       </c>
       <c r="W9" t="n">
-        <v>1099.526722235211</v>
+        <v>115.9155002976577</v>
       </c>
       <c r="X9" t="n">
-        <v>1079.463349058052</v>
+        <v>95.85212712049854</v>
       </c>
       <c r="Y9" t="n">
-        <v>1079.463349058052</v>
+        <v>95.85212712049854</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>424.9775566050018</v>
+        <v>476.3476864762636</v>
       </c>
       <c r="C10" t="n">
-        <v>550.9795624234375</v>
+        <v>602.3496922946994</v>
       </c>
       <c r="D10" t="n">
-        <v>550.9795624234375</v>
+        <v>715.6688364196995</v>
       </c>
       <c r="E10" t="n">
-        <v>550.9795624234375</v>
+        <v>715.6688364196995</v>
       </c>
       <c r="F10" t="n">
-        <v>550.9795624234375</v>
+        <v>840.0298090116349</v>
       </c>
       <c r="G10" t="n">
-        <v>550.9795624234375</v>
+        <v>840.0298090116349</v>
       </c>
       <c r="H10" t="n">
-        <v>652.7906108062779</v>
+        <v>1011.181257449721</v>
       </c>
       <c r="I10" t="n">
-        <v>879.4532726931805</v>
+        <v>1011.181257449721</v>
       </c>
       <c r="J10" t="n">
-        <v>1249.71327269318</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="K10" t="n">
         <v>1381.441257449721</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T10" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="U10" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="V10" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="W10" t="n">
-        <v>201.8109182596774</v>
+        <v>102.1502571067457</v>
       </c>
       <c r="X10" t="n">
-        <v>201.8109182596774</v>
+        <v>253.1810481309392</v>
       </c>
       <c r="Y10" t="n">
-        <v>313.2202189387096</v>
+        <v>364.5903488099714</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>597.4524900262056</v>
+        <v>593.3418560482351</v>
       </c>
       <c r="C11" t="n">
-        <v>467.6801887706562</v>
+        <v>463.5695547926856</v>
       </c>
       <c r="D11" t="n">
-        <v>377.4386173162624</v>
+        <v>373.3279833382919</v>
       </c>
       <c r="E11" t="n">
-        <v>293.2332742790214</v>
+        <v>289.1226403010508</v>
       </c>
       <c r="F11" t="n">
-        <v>208.4962755840599</v>
+        <v>204.3856416060893</v>
       </c>
       <c r="G11" t="n">
-        <v>126.3120357733081</v>
+        <v>122.1973410877592</v>
       </c>
       <c r="H11" t="n">
-        <v>52.85408398404886</v>
+        <v>51.84</v>
       </c>
       <c r="I11" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J11" t="n">
-        <v>134.440205073642</v>
+        <v>560.0241052989622</v>
       </c>
       <c r="K11" t="n">
-        <v>361.7949717483709</v>
+        <v>983.3962097955311</v>
       </c>
       <c r="L11" t="n">
-        <v>1004.304971748371</v>
+        <v>1200.704274318144</v>
       </c>
       <c r="M11" t="n">
-        <v>1646.814971748371</v>
+        <v>1200.704274318144</v>
       </c>
       <c r="N11" t="n">
-        <v>1646.814971748371</v>
+        <v>1200.704274318144</v>
       </c>
       <c r="O11" t="n">
-        <v>1809.956778005698</v>
+        <v>1363.175512284014</v>
       </c>
       <c r="P11" t="n">
-        <v>2008.265727912157</v>
+        <v>2004.695512284016</v>
       </c>
       <c r="Q11" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R11" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="S11" t="n">
-        <v>2452.504870855986</v>
+        <v>2448.412337482045</v>
       </c>
       <c r="T11" t="n">
-        <v>2190.313881748914</v>
+        <v>2186.203572627549</v>
       </c>
       <c r="U11" t="n">
-        <v>1858.889943810872</v>
+        <v>1854.779309832902</v>
       </c>
       <c r="V11" t="n">
-        <v>1546.919212329232</v>
+        <v>1542.808578351262</v>
       </c>
       <c r="W11" t="n">
-        <v>1226.339943661608</v>
+        <v>1222.229309683638</v>
       </c>
       <c r="X11" t="n">
-        <v>952.3178896609338</v>
+        <v>948.2072556829633</v>
       </c>
       <c r="Y11" t="n">
-        <v>760.0780586682001</v>
+        <v>755.9674246902296</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>353.3927448715644</v>
+        <v>350.1145370223171</v>
       </c>
       <c r="C12" t="n">
-        <v>312.8877828053833</v>
+        <v>127.8215785116038</v>
       </c>
       <c r="D12" t="n">
-        <v>285.6779980602291</v>
+        <v>100.6117937664497</v>
       </c>
       <c r="E12" t="n">
-        <v>263.7869907653678</v>
+        <v>78.72078647158841</v>
       </c>
       <c r="F12" t="n">
-        <v>244.9625035553912</v>
+        <v>59.89629926161179</v>
       </c>
       <c r="G12" t="n">
-        <v>240.9290101043439</v>
+        <v>55.86063314046731</v>
       </c>
       <c r="H12" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I12" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J12" t="n">
-        <v>245.6876497036009</v>
+        <v>245.4064648922801</v>
       </c>
       <c r="K12" t="n">
-        <v>554.1988055149654</v>
+        <v>553.5737638168522</v>
       </c>
       <c r="L12" t="n">
-        <v>985.9874996573354</v>
+        <v>984.9000999403543</v>
       </c>
       <c r="M12" t="n">
-        <v>1259.291891400195</v>
+        <v>1257.664941683214</v>
       </c>
       <c r="N12" t="n">
-        <v>1584.75128421531</v>
+        <v>1582.57050421531</v>
       </c>
       <c r="O12" t="n">
-        <v>1999.600074672614</v>
+        <v>1996.91264816318</v>
       </c>
       <c r="P12" t="n">
-        <v>2253.229505368536</v>
+        <v>2250.135450368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2253.229505368536</v>
+        <v>2250.135450368536</v>
       </c>
       <c r="R12" t="n">
-        <v>1747.236647421212</v>
+        <v>2068.250120532513</v>
       </c>
       <c r="S12" t="n">
-        <v>1614.205972785717</v>
+        <v>1935.179089502888</v>
       </c>
       <c r="T12" t="n">
-        <v>1532.034921584493</v>
+        <v>1852.999280916492</v>
       </c>
       <c r="U12" t="n">
-        <v>1452.074056951562</v>
+        <v>1773.038273344739</v>
       </c>
       <c r="V12" t="n">
-        <v>1033.376413323763</v>
+        <v>1354.34062971694</v>
       </c>
       <c r="W12" t="n">
-        <v>920.8782891724215</v>
+        <v>917.6000813231742</v>
       </c>
       <c r="X12" t="n">
-        <v>496.7745119548583</v>
+        <v>493.496304105611</v>
       </c>
       <c r="Y12" t="n">
-        <v>417.591286938561</v>
+        <v>414.3130790893136</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>681.5388756890411</v>
+        <v>683.4428537532905</v>
       </c>
       <c r="C13" t="n">
-        <v>729.3308815074769</v>
+        <v>731.2348595717262</v>
       </c>
       <c r="D13" t="n">
-        <v>764.4400256324769</v>
+        <v>766.3440036967263</v>
       </c>
       <c r="E13" t="n">
-        <v>804.0589298438899</v>
+        <v>805.9629079081393</v>
       </c>
       <c r="F13" t="n">
-        <v>850.2099024358254</v>
+        <v>852.1138805000747</v>
       </c>
       <c r="G13" t="n">
-        <v>926.0259486505795</v>
+        <v>927.9281414689273</v>
       </c>
       <c r="H13" t="n">
-        <v>1022.840277088666</v>
+        <v>1024.726597447997</v>
       </c>
       <c r="I13" t="n">
-        <v>1184.392618975568</v>
+        <v>1186.225252121785</v>
       </c>
       <c r="J13" t="n">
-        <v>1511.063618808347</v>
+        <v>1512.770035069318</v>
       </c>
       <c r="K13" t="n">
-        <v>1615.190403564888</v>
+        <v>1616.689406711104</v>
       </c>
       <c r="L13" t="n">
-        <v>1605.576770221213</v>
+        <v>1606.804966942525</v>
       </c>
       <c r="M13" t="n">
-        <v>1503.006687499644</v>
+        <v>1503.949356815756</v>
       </c>
       <c r="N13" t="n">
-        <v>1347.016646241608</v>
+        <v>1347.680577356031</v>
       </c>
       <c r="O13" t="n">
-        <v>1113.682925280855</v>
+        <v>1114.089396550933</v>
       </c>
       <c r="P13" t="n">
-        <v>819.9781109568783</v>
+        <v>820.1642808525564</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.9758216380924</v>
+        <v>464.0094662812452</v>
       </c>
       <c r="R13" t="n">
-        <v>82.69634147829413</v>
+        <v>82.64808514446405</v>
       </c>
       <c r="S13" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T13" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3449217817557</v>
       </c>
       <c r="U13" t="n">
-        <v>327.6791351738997</v>
+        <v>332.7198068790588</v>
       </c>
       <c r="V13" t="n">
-        <v>448.2905280598457</v>
+        <v>453.3311997650047</v>
       </c>
       <c r="W13" t="n">
-        <v>541.9714463195231</v>
+        <v>547.0121180246822</v>
       </c>
       <c r="X13" t="n">
-        <v>614.7922373437167</v>
+        <v>619.8329090488758</v>
       </c>
       <c r="Y13" t="n">
-        <v>647.991538022749</v>
+        <v>649.8955160869983</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>596.5184060421568</v>
+        <v>596.4384060421568</v>
       </c>
       <c r="C14" t="n">
-        <v>466.7461047866074</v>
+        <v>466.6661047866074</v>
       </c>
       <c r="D14" t="n">
-        <v>376.5045333322136</v>
+        <v>376.4245333322136</v>
       </c>
       <c r="E14" t="n">
-        <v>292.2991902949726</v>
+        <v>292.2191902949726</v>
       </c>
       <c r="F14" t="n">
-        <v>207.5621916000111</v>
+        <v>207.4821916000111</v>
       </c>
       <c r="G14" t="n">
-        <v>125.3779517892592</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H14" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I14" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J14" t="n">
-        <v>134.440205073642</v>
+        <v>560.3618942939371</v>
       </c>
       <c r="K14" t="n">
-        <v>776.950205073642</v>
+        <v>1201.881894293937</v>
       </c>
       <c r="L14" t="n">
-        <v>1419.460205073642</v>
+        <v>1843.401894293937</v>
       </c>
       <c r="M14" t="n">
-        <v>2061.970205073642</v>
+        <v>2230.549243836214</v>
       </c>
       <c r="N14" t="n">
-        <v>2234.549243836214</v>
+        <v>2230.549243836214</v>
       </c>
       <c r="O14" t="n">
-        <v>2397.691050093541</v>
+        <v>2393.691050093541</v>
       </c>
       <c r="P14" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="Q14" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R14" t="n">
-        <v>2595.065916015951</v>
+        <v>2592</v>
       </c>
       <c r="S14" t="n">
-        <v>2451.570786871937</v>
+        <v>2451.490786871937</v>
       </c>
       <c r="T14" t="n">
-        <v>2189.379797764865</v>
+        <v>2189.299797764865</v>
       </c>
       <c r="U14" t="n">
-        <v>1857.955859826824</v>
+        <v>1857.875859826824</v>
       </c>
       <c r="V14" t="n">
-        <v>1545.985128345183</v>
+        <v>1545.905128345183</v>
       </c>
       <c r="W14" t="n">
-        <v>1225.405859677559</v>
+        <v>1225.325859677559</v>
       </c>
       <c r="X14" t="n">
-        <v>951.383805676885</v>
+        <v>951.3038056768851</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.1439746841513</v>
+        <v>759.0639746841513</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>353.3927448715644</v>
+        <v>1326.040017598837</v>
       </c>
       <c r="C15" t="n">
-        <v>127.87842242241</v>
+        <v>1100.525695149683</v>
       </c>
       <c r="D15" t="n">
-        <v>100.6686376772558</v>
+        <v>749.0734861621044</v>
       </c>
       <c r="E15" t="n">
-        <v>78.77763038239456</v>
+        <v>402.9400546248189</v>
       </c>
       <c r="F15" t="n">
-        <v>59.95314317241794</v>
+        <v>59.87314317241794</v>
       </c>
       <c r="G15" t="n">
-        <v>55.91964972137069</v>
+        <v>55.83964972137069</v>
       </c>
       <c r="H15" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I15" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J15" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K15" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L15" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M15" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N15" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O15" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P15" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R15" t="n">
-        <v>2071.479071663636</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S15" t="n">
-        <v>1938.448397028141</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T15" t="n">
-        <v>1856.277345826917</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U15" t="n">
-        <v>1776.316481193986</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V15" t="n">
-        <v>1681.861261808612</v>
+        <v>1681.781261808612</v>
       </c>
       <c r="W15" t="n">
-        <v>1569.36313765727</v>
+        <v>1569.28313765727</v>
       </c>
       <c r="X15" t="n">
-        <v>1145.259360439707</v>
+        <v>1469.421784682131</v>
       </c>
       <c r="Y15" t="n">
-        <v>741.8337111809852</v>
+        <v>1390.238559665834</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>681.5388756890411</v>
+        <v>681.4588756890412</v>
       </c>
       <c r="C16" t="n">
-        <v>729.3308815074769</v>
+        <v>729.2508815074769</v>
       </c>
       <c r="D16" t="n">
-        <v>764.4400256324769</v>
+        <v>764.360025632477</v>
       </c>
       <c r="E16" t="n">
-        <v>804.0589298438899</v>
+        <v>803.97892984389</v>
       </c>
       <c r="F16" t="n">
-        <v>850.2099024358254</v>
+        <v>850.1299024358254</v>
       </c>
       <c r="G16" t="n">
-        <v>926.0259486505795</v>
+        <v>925.9459486505796</v>
       </c>
       <c r="H16" t="n">
-        <v>1022.840277088666</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I16" t="n">
-        <v>1184.392618975568</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J16" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K16" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L16" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M16" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N16" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O16" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P16" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568782</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380923</v>
       </c>
       <c r="R16" t="n">
-        <v>82.69634147829412</v>
+        <v>82.61634147829412</v>
       </c>
       <c r="S16" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T16" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506081</v>
       </c>
       <c r="U16" t="n">
-        <v>332.8075321249603</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V16" t="n">
-        <v>448.2905280598457</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W16" t="n">
-        <v>541.9714463195231</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X16" t="n">
-        <v>614.7922373437167</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y16" t="n">
-        <v>647.991538022749</v>
+        <v>647.911538022749</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>597.4524900262059</v>
+        <v>593.4524900262059</v>
       </c>
       <c r="C17" t="n">
-        <v>467.6801887706564</v>
+        <v>463.6801887706564</v>
       </c>
       <c r="D17" t="n">
-        <v>377.4386173162627</v>
+        <v>373.4386173162627</v>
       </c>
       <c r="E17" t="n">
-        <v>293.2332742790216</v>
+        <v>289.2332742790216</v>
       </c>
       <c r="F17" t="n">
-        <v>208.4962755840601</v>
+        <v>204.4962755840601</v>
       </c>
       <c r="G17" t="n">
-        <v>126.3120357733083</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H17" t="n">
-        <v>52.85408398404904</v>
+        <v>51.84</v>
       </c>
       <c r="I17" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J17" t="n">
-        <v>560.4418942939371</v>
+        <v>560.3618942939371</v>
       </c>
       <c r="K17" t="n">
-        <v>1202.951894293937</v>
+        <v>927.8820712301057</v>
       </c>
       <c r="L17" t="n">
-        <v>1592.039243836214</v>
+        <v>1145.818193742669</v>
       </c>
       <c r="M17" t="n">
-        <v>2234.549243836214</v>
+        <v>1145.818193742669</v>
       </c>
       <c r="N17" t="n">
-        <v>2234.549243836214</v>
+        <v>1787.338193742671</v>
       </c>
       <c r="O17" t="n">
-        <v>2397.691050093541</v>
+        <v>1950.479999999998</v>
       </c>
       <c r="P17" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="Q17" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R17" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="S17" t="n">
-        <v>2452.504870855986</v>
+        <v>2448.504870855986</v>
       </c>
       <c r="T17" t="n">
-        <v>2190.313881748914</v>
+        <v>2186.313881748914</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.889943810873</v>
+        <v>1854.889943810873</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.919212329232</v>
+        <v>1542.919212329232</v>
       </c>
       <c r="W17" t="n">
-        <v>1226.339943661608</v>
+        <v>1222.339943661608</v>
       </c>
       <c r="X17" t="n">
-        <v>952.317889660934</v>
+        <v>948.317889660934</v>
       </c>
       <c r="Y17" t="n">
-        <v>760.0780586682004</v>
+        <v>756.0780586682004</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1326.120017598837</v>
+        <v>168.3033844885911</v>
       </c>
       <c r="C18" t="n">
-        <v>1100.605695149683</v>
+        <v>127.79842242241</v>
       </c>
       <c r="D18" t="n">
-        <v>749.1534861621044</v>
+        <v>100.5886376772558</v>
       </c>
       <c r="E18" t="n">
-        <v>403.0200546248188</v>
+        <v>78.69763038239458</v>
       </c>
       <c r="F18" t="n">
-        <v>59.95314317241794</v>
+        <v>59.87314317241794</v>
       </c>
       <c r="G18" t="n">
-        <v>55.91964972137069</v>
+        <v>55.83964972137069</v>
       </c>
       <c r="H18" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I18" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J18" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K18" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L18" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M18" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N18" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O18" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P18" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R18" t="n">
-        <v>2071.479071663636</v>
+        <v>1886.389711280663</v>
       </c>
       <c r="S18" t="n">
-        <v>1938.448397028141</v>
+        <v>1753.359036645168</v>
       </c>
       <c r="T18" t="n">
-        <v>1856.277345826917</v>
+        <v>1671.187985443944</v>
       </c>
       <c r="U18" t="n">
-        <v>1776.316481193986</v>
+        <v>1266.984696568589</v>
       </c>
       <c r="V18" t="n">
-        <v>1681.861261808612</v>
+        <v>848.2870529407903</v>
       </c>
       <c r="W18" t="n">
-        <v>1569.36313765727</v>
+        <v>411.546504547024</v>
       </c>
       <c r="X18" t="n">
-        <v>1469.501784682131</v>
+        <v>311.6851515718851</v>
       </c>
       <c r="Y18" t="n">
-        <v>1390.318559665834</v>
+        <v>232.5019265555877</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>686.6672726401017</v>
+        <v>681.4588756890412</v>
       </c>
       <c r="C19" t="n">
-        <v>734.4592784585375</v>
+        <v>729.2508815074769</v>
       </c>
       <c r="D19" t="n">
-        <v>769.5684225835375</v>
+        <v>764.360025632477</v>
       </c>
       <c r="E19" t="n">
-        <v>809.1873267949505</v>
+        <v>803.97892984389</v>
       </c>
       <c r="F19" t="n">
-        <v>855.338299386886</v>
+        <v>850.1299024358254</v>
       </c>
       <c r="G19" t="n">
-        <v>931.1543456016401</v>
+        <v>925.9459486505796</v>
       </c>
       <c r="H19" t="n">
-        <v>1027.968674039726</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I19" t="n">
-        <v>1189.521015926629</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J19" t="n">
-        <v>1516.192015759408</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K19" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L19" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M19" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N19" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O19" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568782</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380923</v>
       </c>
       <c r="R19" t="n">
-        <v>82.69634147829412</v>
+        <v>82.61634147829412</v>
       </c>
       <c r="S19" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T19" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506081</v>
       </c>
       <c r="U19" t="n">
-        <v>332.8075321249603</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V19" t="n">
-        <v>453.4189250109063</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W19" t="n">
-        <v>547.0998432705837</v>
+        <v>541.8914463195232</v>
       </c>
       <c r="X19" t="n">
-        <v>619.9206342947773</v>
+        <v>614.7122373437168</v>
       </c>
       <c r="Y19" t="n">
-        <v>653.1199349738096</v>
+        <v>647.911538022749</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>597.4524900262056</v>
+        <v>596.4384060421568</v>
       </c>
       <c r="C20" t="n">
-        <v>467.6801887706562</v>
+        <v>466.6661047866074</v>
       </c>
       <c r="D20" t="n">
-        <v>377.4386173162624</v>
+        <v>376.4245333322136</v>
       </c>
       <c r="E20" t="n">
-        <v>293.2332742790214</v>
+        <v>292.2191902949726</v>
       </c>
       <c r="F20" t="n">
-        <v>208.4962755840599</v>
+        <v>207.4821916000111</v>
       </c>
       <c r="G20" t="n">
-        <v>126.3120357733081</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H20" t="n">
-        <v>52.85408398404886</v>
+        <v>51.84</v>
       </c>
       <c r="I20" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J20" t="n">
-        <v>134.440205073642</v>
+        <v>560.3618942939371</v>
       </c>
       <c r="K20" t="n">
-        <v>776.950205073642</v>
+        <v>1201.881894293937</v>
       </c>
       <c r="L20" t="n">
-        <v>1419.460205073642</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="M20" t="n">
-        <v>2061.970205073642</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="N20" t="n">
-        <v>2234.549243836214</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="O20" t="n">
-        <v>2397.691050093541</v>
+        <v>1805.956778005698</v>
       </c>
       <c r="P20" t="n">
-        <v>2596</v>
+        <v>2004.265727912157</v>
       </c>
       <c r="Q20" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R20" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="S20" t="n">
-        <v>2452.504870855986</v>
+        <v>2451.490786871937</v>
       </c>
       <c r="T20" t="n">
-        <v>2190.313881748914</v>
+        <v>2189.299797764865</v>
       </c>
       <c r="U20" t="n">
-        <v>1858.889943810872</v>
+        <v>1857.875859826824</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.919212329232</v>
+        <v>1545.905128345183</v>
       </c>
       <c r="W20" t="n">
-        <v>1226.339943661608</v>
+        <v>1225.325859677559</v>
       </c>
       <c r="X20" t="n">
-        <v>952.3178896609338</v>
+        <v>951.3038056768851</v>
       </c>
       <c r="Y20" t="n">
-        <v>760.0780586682001</v>
+        <v>759.0639746841513</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1326.120017598837</v>
+        <v>353.3127448715645</v>
       </c>
       <c r="C21" t="n">
-        <v>1100.605695149683</v>
+        <v>312.8077828053833</v>
       </c>
       <c r="D21" t="n">
-        <v>749.1534861621044</v>
+        <v>285.5979980602291</v>
       </c>
       <c r="E21" t="n">
-        <v>403.0200546248188</v>
+        <v>263.7069907653679</v>
       </c>
       <c r="F21" t="n">
-        <v>59.95314317241791</v>
+        <v>244.8825035553913</v>
       </c>
       <c r="G21" t="n">
-        <v>55.91964972137067</v>
+        <v>55.83964972137069</v>
       </c>
       <c r="H21" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I21" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J21" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K21" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L21" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M21" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N21" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O21" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P21" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R21" t="n">
-        <v>2071.479071663636</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S21" t="n">
-        <v>1938.448397028141</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T21" t="n">
-        <v>1856.277345826917</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U21" t="n">
-        <v>1776.316481193986</v>
+        <v>1451.994056951562</v>
       </c>
       <c r="V21" t="n">
-        <v>1681.861261808612</v>
+        <v>1033.296413323764</v>
       </c>
       <c r="W21" t="n">
-        <v>1569.36313765727</v>
+        <v>596.5558649299974</v>
       </c>
       <c r="X21" t="n">
-        <v>1469.501784682131</v>
+        <v>496.6945119548584</v>
       </c>
       <c r="Y21" t="n">
-        <v>1390.318559665834</v>
+        <v>417.5112869385611</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>681.5388756890411</v>
+        <v>681.4588756890412</v>
       </c>
       <c r="C22" t="n">
-        <v>729.3308815074769</v>
+        <v>729.2508815074769</v>
       </c>
       <c r="D22" t="n">
-        <v>764.4400256324769</v>
+        <v>764.360025632477</v>
       </c>
       <c r="E22" t="n">
-        <v>804.0589298438899</v>
+        <v>803.97892984389</v>
       </c>
       <c r="F22" t="n">
-        <v>850.2099024358254</v>
+        <v>850.1299024358254</v>
       </c>
       <c r="G22" t="n">
-        <v>926.0259486505795</v>
+        <v>925.9459486505796</v>
       </c>
       <c r="H22" t="n">
-        <v>1022.840277088666</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I22" t="n">
-        <v>1184.392618975568</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J22" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K22" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L22" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M22" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N22" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O22" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568782</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380923</v>
       </c>
       <c r="R22" t="n">
-        <v>82.69634147829413</v>
+        <v>82.61634147829412</v>
       </c>
       <c r="S22" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T22" t="n">
-        <v>164.4325496506081</v>
+        <v>159.2241526995476</v>
       </c>
       <c r="U22" t="n">
-        <v>332.8075321249603</v>
+        <v>327.5991351738998</v>
       </c>
       <c r="V22" t="n">
-        <v>453.4189250109063</v>
+        <v>448.2105280598458</v>
       </c>
       <c r="W22" t="n">
-        <v>547.0998432705837</v>
+        <v>541.8914463195232</v>
       </c>
       <c r="X22" t="n">
-        <v>614.7922373437167</v>
+        <v>614.7122373437168</v>
       </c>
       <c r="Y22" t="n">
-        <v>647.991538022749</v>
+        <v>647.911538022749</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>597.4524900262056</v>
+        <v>593.4524900262056</v>
       </c>
       <c r="C23" t="n">
-        <v>467.6801887706562</v>
+        <v>463.6801887706562</v>
       </c>
       <c r="D23" t="n">
-        <v>377.4386173162624</v>
+        <v>373.4386173162624</v>
       </c>
       <c r="E23" t="n">
-        <v>293.2332742790214</v>
+        <v>289.2332742790214</v>
       </c>
       <c r="F23" t="n">
-        <v>208.4962755840599</v>
+        <v>204.4962755840599</v>
       </c>
       <c r="G23" t="n">
-        <v>126.3120357733081</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H23" t="n">
-        <v>52.85408398404886</v>
+        <v>51.84</v>
       </c>
       <c r="I23" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J23" t="n">
-        <v>134.440205073642</v>
+        <v>134.360205073642</v>
       </c>
       <c r="K23" t="n">
-        <v>776.950205073642</v>
+        <v>775.8802050736419</v>
       </c>
       <c r="L23" t="n">
-        <v>994.8863275862049</v>
+        <v>1417.400205073642</v>
       </c>
       <c r="M23" t="n">
-        <v>1592.039243836214</v>
+        <v>2058.920205073644</v>
       </c>
       <c r="N23" t="n">
-        <v>2234.549243836214</v>
+        <v>2230.549243836214</v>
       </c>
       <c r="O23" t="n">
-        <v>2397.691050093541</v>
+        <v>2393.691050093541</v>
       </c>
       <c r="P23" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="Q23" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R23" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="S23" t="n">
-        <v>2452.504870855986</v>
+        <v>2448.504870855986</v>
       </c>
       <c r="T23" t="n">
-        <v>2190.313881748914</v>
+        <v>2186.313881748914</v>
       </c>
       <c r="U23" t="n">
-        <v>1858.889943810872</v>
+        <v>1854.889943810872</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.919212329232</v>
+        <v>1542.919212329232</v>
       </c>
       <c r="W23" t="n">
-        <v>1226.339943661608</v>
+        <v>1222.339943661608</v>
       </c>
       <c r="X23" t="n">
-        <v>952.3178896609338</v>
+        <v>948.3178896609338</v>
       </c>
       <c r="Y23" t="n">
-        <v>760.0780586682001</v>
+        <v>756.0780586682001</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1326.120017598837</v>
+        <v>816.7882329734394</v>
       </c>
       <c r="C24" t="n">
-        <v>1100.605695149683</v>
+        <v>776.2832709072584</v>
       </c>
       <c r="D24" t="n">
-        <v>749.1534861621044</v>
+        <v>749.0734861621042</v>
       </c>
       <c r="E24" t="n">
-        <v>403.0200546248188</v>
+        <v>402.9400546248188</v>
       </c>
       <c r="F24" t="n">
-        <v>59.95314317241791</v>
+        <v>59.87314317241791</v>
       </c>
       <c r="G24" t="n">
-        <v>55.91964972137067</v>
+        <v>55.83964972137068</v>
       </c>
       <c r="H24" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I24" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J24" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K24" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L24" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M24" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N24" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O24" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P24" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R24" t="n">
-        <v>2071.479071663636</v>
+        <v>1747.156647421212</v>
       </c>
       <c r="S24" t="n">
-        <v>1938.448397028141</v>
+        <v>1429.116612402743</v>
       </c>
       <c r="T24" t="n">
-        <v>1856.277345826917</v>
+        <v>1346.945561201519</v>
       </c>
       <c r="U24" t="n">
-        <v>1776.316481193986</v>
+        <v>1266.984696568588</v>
       </c>
       <c r="V24" t="n">
-        <v>1681.861261808612</v>
+        <v>1172.529477183214</v>
       </c>
       <c r="W24" t="n">
-        <v>1569.36313765727</v>
+        <v>1060.031353031872</v>
       </c>
       <c r="X24" t="n">
-        <v>1469.501784682131</v>
+        <v>960.1700000567333</v>
       </c>
       <c r="Y24" t="n">
-        <v>1390.318559665834</v>
+        <v>880.986775040436</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>681.5388756890411</v>
+        <v>686.5872726401018</v>
       </c>
       <c r="C25" t="n">
-        <v>729.3308815074769</v>
+        <v>734.3792784585376</v>
       </c>
       <c r="D25" t="n">
-        <v>764.4400256324769</v>
+        <v>769.4884225835376</v>
       </c>
       <c r="E25" t="n">
-        <v>804.0589298438899</v>
+        <v>809.1073267949506</v>
       </c>
       <c r="F25" t="n">
-        <v>850.2099024358254</v>
+        <v>855.2582993868861</v>
       </c>
       <c r="G25" t="n">
-        <v>926.0259486505795</v>
+        <v>931.0743456016402</v>
       </c>
       <c r="H25" t="n">
-        <v>1022.840277088666</v>
+        <v>1027.888674039726</v>
       </c>
       <c r="I25" t="n">
-        <v>1184.392618975568</v>
+        <v>1189.441015926629</v>
       </c>
       <c r="J25" t="n">
-        <v>1511.063618808347</v>
+        <v>1516.112015759408</v>
       </c>
       <c r="K25" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L25" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M25" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N25" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O25" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568782</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380924</v>
       </c>
       <c r="R25" t="n">
-        <v>82.69634147829413</v>
+        <v>82.61634147829413</v>
       </c>
       <c r="S25" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T25" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506081</v>
       </c>
       <c r="U25" t="n">
-        <v>332.8075321249603</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V25" t="n">
-        <v>453.4189250109063</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W25" t="n">
-        <v>547.0998432705837</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X25" t="n">
-        <v>614.7922373437167</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y25" t="n">
-        <v>647.991538022749</v>
+        <v>653.0399349738096</v>
       </c>
     </row>
     <row r="26">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>601.4524900262056</v>
+        <v>601.4524900262059</v>
       </c>
       <c r="C26" t="n">
-        <v>471.6801887706562</v>
+        <v>471.6801887706564</v>
       </c>
       <c r="D26" t="n">
-        <v>381.4386173162624</v>
+        <v>381.4386173162627</v>
       </c>
       <c r="E26" t="n">
-        <v>297.2332742790214</v>
+        <v>297.2332742790216</v>
       </c>
       <c r="F26" t="n">
-        <v>212.4962755840599</v>
+        <v>212.4962755840601</v>
       </c>
       <c r="G26" t="n">
-        <v>130.3120357733081</v>
+        <v>130.3120357733083</v>
       </c>
       <c r="H26" t="n">
         <v>52</v>
@@ -6217,25 +6217,25 @@
         <v>52</v>
       </c>
       <c r="J26" t="n">
-        <v>134.520205073642</v>
+        <v>560.5218942939371</v>
       </c>
       <c r="K26" t="n">
-        <v>310.1917798977626</v>
+        <v>1204.021894293937</v>
       </c>
       <c r="L26" t="n">
-        <v>951.5492438362139</v>
+        <v>1650.814971748371</v>
       </c>
       <c r="M26" t="n">
-        <v>1595.049243836214</v>
+        <v>1650.814971748371</v>
       </c>
       <c r="N26" t="n">
-        <v>2238.549243836214</v>
+        <v>1650.814971748371</v>
       </c>
       <c r="O26" t="n">
-        <v>2401.691050093541</v>
+        <v>1813.956778005698</v>
       </c>
       <c r="P26" t="n">
-        <v>2600</v>
+        <v>2012.265727912157</v>
       </c>
       <c r="Q26" t="n">
         <v>2600</v>
@@ -6250,7 +6250,7 @@
         <v>2194.313881748914</v>
       </c>
       <c r="U26" t="n">
-        <v>1862.889943810872</v>
+        <v>1862.889943810873</v>
       </c>
       <c r="V26" t="n">
         <v>1550.919212329232</v>
@@ -6259,10 +6259,10 @@
         <v>1230.339943661608</v>
       </c>
       <c r="X26" t="n">
-        <v>956.3178896609338</v>
+        <v>956.317889660934</v>
       </c>
       <c r="Y26" t="n">
-        <v>764.0780586682001</v>
+        <v>764.0780586682004</v>
       </c>
     </row>
     <row r="27">
@@ -6272,7 +6272,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>353.4727448715643</v>
+        <v>168.4633844885911</v>
       </c>
       <c r="C27" t="n">
         <v>127.95842242241</v>
@@ -6281,13 +6281,13 @@
         <v>100.7486376772558</v>
       </c>
       <c r="E27" t="n">
-        <v>78.85763038239455</v>
+        <v>78.85763038239458</v>
       </c>
       <c r="F27" t="n">
-        <v>60.03314317241791</v>
+        <v>60.03314317241794</v>
       </c>
       <c r="G27" t="n">
-        <v>55.99964972137067</v>
+        <v>55.99964972137069</v>
       </c>
       <c r="H27" t="n">
         <v>52</v>
@@ -6329,19 +6329,19 @@
         <v>1856.357345826917</v>
       </c>
       <c r="U27" t="n">
-        <v>1452.154056951562</v>
+        <v>1776.396481193986</v>
       </c>
       <c r="V27" t="n">
         <v>1357.698837566188</v>
       </c>
       <c r="W27" t="n">
-        <v>1245.200713414846</v>
+        <v>920.9582891724215</v>
       </c>
       <c r="X27" t="n">
-        <v>1145.339360439707</v>
+        <v>496.8545119548583</v>
       </c>
       <c r="Y27" t="n">
-        <v>741.9137111809852</v>
+        <v>417.6712869385609</v>
       </c>
     </row>
     <row r="28">
@@ -6399,7 +6399,7 @@
         <v>464.0558216380924</v>
       </c>
       <c r="R28" t="n">
-        <v>82.77634147829413</v>
+        <v>82.77634147829411</v>
       </c>
       <c r="S28" t="n">
         <v>52</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>601.4524900262056</v>
+        <v>596.5984060421567</v>
       </c>
       <c r="C29" t="n">
-        <v>471.6801887706562</v>
+        <v>466.8261047866073</v>
       </c>
       <c r="D29" t="n">
-        <v>381.4386173162624</v>
+        <v>376.5845333322136</v>
       </c>
       <c r="E29" t="n">
-        <v>297.2332742790214</v>
+        <v>292.3791902949725</v>
       </c>
       <c r="F29" t="n">
-        <v>212.4962755840599</v>
+        <v>207.642191600011</v>
       </c>
       <c r="G29" t="n">
-        <v>130.3120357733081</v>
+        <v>125.4579517892592</v>
       </c>
       <c r="H29" t="n">
         <v>52</v>
@@ -6454,19 +6454,19 @@
         <v>52</v>
       </c>
       <c r="J29" t="n">
-        <v>134.520205073642</v>
+        <v>560.5218942939371</v>
       </c>
       <c r="K29" t="n">
-        <v>778.020205073642</v>
+        <v>1204.021894293937</v>
       </c>
       <c r="L29" t="n">
-        <v>1114.691050093541</v>
+        <v>1847.521894293937</v>
       </c>
       <c r="M29" t="n">
-        <v>1114.691050093541</v>
+        <v>2238.549243836214</v>
       </c>
       <c r="N29" t="n">
-        <v>1758.191050093541</v>
+        <v>2238.549243836214</v>
       </c>
       <c r="O29" t="n">
         <v>2401.691050093541</v>
@@ -6509,10 +6509,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>816.9482329734396</v>
+        <v>168.4633844885911</v>
       </c>
       <c r="C30" t="n">
-        <v>452.2008466648342</v>
+        <v>127.95842242241</v>
       </c>
       <c r="D30" t="n">
         <v>100.7486376772558</v>
@@ -6569,16 +6569,16 @@
         <v>1776.396481193986</v>
       </c>
       <c r="V30" t="n">
-        <v>1681.941261808612</v>
+        <v>1357.698837566188</v>
       </c>
       <c r="W30" t="n">
-        <v>1569.44313765727</v>
+        <v>920.9582891724215</v>
       </c>
       <c r="X30" t="n">
-        <v>1469.581784682131</v>
+        <v>496.8545119548583</v>
       </c>
       <c r="Y30" t="n">
-        <v>1205.389199282861</v>
+        <v>232.6619265555877</v>
       </c>
     </row>
     <row r="31">
@@ -6645,16 +6645,16 @@
         <v>164.5125496506082</v>
       </c>
       <c r="U31" t="n">
-        <v>332.8875321249603</v>
+        <v>327.7591351738997</v>
       </c>
       <c r="V31" t="n">
-        <v>453.4989250109063</v>
+        <v>448.3705280598456</v>
       </c>
       <c r="W31" t="n">
-        <v>547.1798432705837</v>
+        <v>542.0514463195231</v>
       </c>
       <c r="X31" t="n">
-        <v>620.0006342947772</v>
+        <v>614.8722373437166</v>
       </c>
       <c r="Y31" t="n">
         <v>648.0715380227489</v>
@@ -6667,25 +6667,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>601.4524900262059</v>
+        <v>601.4524900262056</v>
       </c>
       <c r="C32" t="n">
-        <v>471.6801887706564</v>
+        <v>471.6801887706562</v>
       </c>
       <c r="D32" t="n">
-        <v>381.4386173162627</v>
+        <v>381.4386173162624</v>
       </c>
       <c r="E32" t="n">
-        <v>297.2332742790216</v>
+        <v>297.2332742790214</v>
       </c>
       <c r="F32" t="n">
-        <v>212.4962755840601</v>
+        <v>212.4962755840599</v>
       </c>
       <c r="G32" t="n">
-        <v>130.3120357733083</v>
+        <v>130.3120357733081</v>
       </c>
       <c r="H32" t="n">
-        <v>56.85408398404904</v>
+        <v>56.85408398404886</v>
       </c>
       <c r="I32" t="n">
         <v>52</v>
@@ -6694,22 +6694,22 @@
         <v>134.520205073642</v>
       </c>
       <c r="K32" t="n">
-        <v>310.1917798977626</v>
+        <v>778.020205073642</v>
       </c>
       <c r="L32" t="n">
-        <v>528.1279024103255</v>
+        <v>1421.520205073642</v>
       </c>
       <c r="M32" t="n">
-        <v>1171.627902410326</v>
+        <v>1595.049243836214</v>
       </c>
       <c r="N32" t="n">
-        <v>1650.814971748371</v>
+        <v>2238.549243836214</v>
       </c>
       <c r="O32" t="n">
-        <v>1813.956778005698</v>
+        <v>2401.691050093541</v>
       </c>
       <c r="P32" t="n">
-        <v>2012.265727912157</v>
+        <v>2600</v>
       </c>
       <c r="Q32" t="n">
         <v>2600</v>
@@ -6724,7 +6724,7 @@
         <v>2194.313881748914</v>
       </c>
       <c r="U32" t="n">
-        <v>1862.889943810873</v>
+        <v>1862.889943810872</v>
       </c>
       <c r="V32" t="n">
         <v>1550.919212329232</v>
@@ -6733,10 +6733,10 @@
         <v>1230.339943661608</v>
       </c>
       <c r="X32" t="n">
-        <v>956.317889660934</v>
+        <v>956.3178896609338</v>
       </c>
       <c r="Y32" t="n">
-        <v>764.0780586682004</v>
+        <v>764.0780586682001</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>168.4633844885911</v>
+        <v>1141.190657215864</v>
       </c>
       <c r="C33" t="n">
-        <v>127.95842242241</v>
+        <v>776.4432709072585</v>
       </c>
       <c r="D33" t="n">
-        <v>100.7486376772558</v>
+        <v>424.9910619196801</v>
       </c>
       <c r="E33" t="n">
-        <v>78.85763038239458</v>
+        <v>78.85763038239455</v>
       </c>
       <c r="F33" t="n">
-        <v>60.03314317241794</v>
+        <v>60.03314317241791</v>
       </c>
       <c r="G33" t="n">
-        <v>55.99964972137069</v>
+        <v>55.99964972137067</v>
       </c>
       <c r="H33" t="n">
         <v>52</v>
@@ -6809,13 +6809,13 @@
         <v>1681.941261808612</v>
       </c>
       <c r="W33" t="n">
-        <v>1384.433777274297</v>
+        <v>1569.44313765727</v>
       </c>
       <c r="X33" t="n">
-        <v>960.3300000567335</v>
+        <v>1469.581784682131</v>
       </c>
       <c r="Y33" t="n">
-        <v>556.9043507980119</v>
+        <v>1205.389199282861</v>
       </c>
     </row>
     <row r="34">
@@ -6873,7 +6873,7 @@
         <v>464.0558216380924</v>
       </c>
       <c r="R34" t="n">
-        <v>82.77634147829411</v>
+        <v>82.77634147829413</v>
       </c>
       <c r="S34" t="n">
         <v>52</v>
@@ -6882,16 +6882,16 @@
         <v>164.5125496506082</v>
       </c>
       <c r="U34" t="n">
-        <v>327.7591351738997</v>
+        <v>332.8875321249603</v>
       </c>
       <c r="V34" t="n">
-        <v>448.3705280598456</v>
+        <v>453.4989250109063</v>
       </c>
       <c r="W34" t="n">
-        <v>542.0514463195231</v>
+        <v>547.1798432705837</v>
       </c>
       <c r="X34" t="n">
-        <v>614.8722373437166</v>
+        <v>620.0006342947772</v>
       </c>
       <c r="Y34" t="n">
         <v>648.0715380227489</v>
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>444.1038605876161</v>
+        <v>444.0238605876114</v>
       </c>
       <c r="C35" t="n">
-        <v>338.5739835744909</v>
+        <v>338.4939835744862</v>
       </c>
       <c r="D35" t="n">
-        <v>272.5748363625214</v>
+        <v>272.4948363625167</v>
       </c>
       <c r="E35" t="n">
-        <v>212.6119175677046</v>
+        <v>212.5319175676998</v>
       </c>
       <c r="F35" t="n">
-        <v>152.1173431151673</v>
+        <v>152.0373431151626</v>
       </c>
       <c r="G35" t="n">
-        <v>94.1755275468397</v>
+        <v>94.09552754683497</v>
       </c>
       <c r="H35" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="I35" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="J35" t="n">
-        <v>553.4818942939419</v>
+        <v>127.400205073642</v>
       </c>
       <c r="K35" t="n">
-        <v>773.7892438363638</v>
+        <v>303.0717798977627</v>
       </c>
       <c r="L35" t="n">
-        <v>1330.169243836422</v>
+        <v>771.769243836203</v>
       </c>
       <c r="M35" t="n">
-        <v>1330.169243836422</v>
+        <v>1327.159243836209</v>
       </c>
       <c r="N35" t="n">
-        <v>1330.169243836422</v>
+        <v>1882.549243836214</v>
       </c>
       <c r="O35" t="n">
-        <v>1493.311050093749</v>
+        <v>2045.691050093541</v>
       </c>
       <c r="P35" t="n">
-        <v>1691.620000000208</v>
+        <v>2244</v>
       </c>
       <c r="Q35" t="n">
-        <v>2248.000000000237</v>
+        <v>2244</v>
       </c>
       <c r="R35" t="n">
-        <v>2248.000000000237</v>
+        <v>2244</v>
       </c>
       <c r="S35" t="n">
-        <v>2128.747295098647</v>
+        <v>2129.379271720421</v>
       </c>
       <c r="T35" t="n">
-        <v>1890.798730233999</v>
+        <v>1891.430706855774</v>
       </c>
       <c r="U35" t="n">
-        <v>1584.329193160162</v>
+        <v>1584.249193160157</v>
       </c>
       <c r="V35" t="n">
-        <v>1296.600885920946</v>
+        <v>1296.520885920941</v>
       </c>
       <c r="W35" t="n">
-        <v>1000.264041495746</v>
+        <v>1000.184041495741</v>
       </c>
       <c r="X35" t="n">
-        <v>750.4844117374957</v>
+        <v>750.404411737491</v>
       </c>
       <c r="Y35" t="n">
-        <v>582.4870049871863</v>
+        <v>582.4070049871816</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>840.372138810963</v>
+        <v>1535.072330412156</v>
       </c>
       <c r="C36" t="n">
-        <v>824.1096009872061</v>
+        <v>1170.324944103551</v>
       </c>
       <c r="D36" t="n">
-        <v>821.1422404844762</v>
+        <v>818.8727351159725</v>
       </c>
       <c r="E36" t="n">
-        <v>475.0088089471907</v>
+        <v>472.739303578687</v>
       </c>
       <c r="F36" t="n">
-        <v>131.9418974947898</v>
+        <v>129.6723921262861</v>
       </c>
       <c r="G36" t="n">
-        <v>131.9418974947898</v>
+        <v>129.6723921262861</v>
       </c>
       <c r="H36" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="I36" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="J36" t="n">
-        <v>238.7276497036056</v>
+        <v>236.458144335102</v>
       </c>
       <c r="K36" t="n">
-        <v>547.2388055149702</v>
+        <v>544.9693001464665</v>
       </c>
       <c r="L36" t="n">
-        <v>979.0274996573402</v>
+        <v>976.7579942888365</v>
       </c>
       <c r="M36" t="n">
-        <v>1252.331891400199</v>
+        <v>1250.062386031696</v>
       </c>
       <c r="N36" t="n">
-        <v>1577.791284215315</v>
+        <v>1575.521778846811</v>
       </c>
       <c r="O36" t="n">
-        <v>1992.640074672619</v>
+        <v>1990.370569304115</v>
       </c>
       <c r="P36" t="n">
-        <v>2246.26950536854</v>
+        <v>2244.000000000037</v>
       </c>
       <c r="Q36" t="n">
-        <v>2246.26950536854</v>
+        <v>2244.000000000037</v>
       </c>
       <c r="R36" t="n">
-        <v>1740.276647421216</v>
+        <v>2086.491990537561</v>
       </c>
       <c r="S36" t="n">
-        <v>1631.488397028146</v>
+        <v>1977.703740144491</v>
       </c>
       <c r="T36" t="n">
-        <v>1225.074921584497</v>
+        <v>1919.775113185691</v>
       </c>
       <c r="U36" t="n">
-        <v>1169.35648119399</v>
+        <v>1864.056672795184</v>
       </c>
       <c r="V36" t="n">
-        <v>1099.143686051041</v>
+        <v>1793.843877652234</v>
       </c>
       <c r="W36" t="n">
-        <v>1010.887986142123</v>
+        <v>1705.588177743316</v>
       </c>
       <c r="X36" t="n">
-        <v>935.2690574094083</v>
+        <v>1629.969249010602</v>
       </c>
       <c r="Y36" t="n">
-        <v>880.3282566355352</v>
+        <v>1575.028448236729</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>267.090594688537</v>
+        <v>366.5866409032864</v>
       </c>
       <c r="C37" t="n">
-        <v>338.6426005069727</v>
+        <v>438.1386467217221</v>
       </c>
       <c r="D37" t="n">
-        <v>397.5117446319728</v>
+        <v>497.0077908467222</v>
       </c>
       <c r="E37" t="n">
-        <v>460.8906488433858</v>
+        <v>560.3866950581353</v>
       </c>
       <c r="F37" t="n">
-        <v>530.8016214353213</v>
+        <v>630.2976676500707</v>
       </c>
       <c r="G37" t="n">
-        <v>630.3776676500754</v>
+        <v>630.2976676500707</v>
       </c>
       <c r="H37" t="n">
-        <v>750.9519960881615</v>
+        <v>750.8719960881568</v>
       </c>
       <c r="I37" t="n">
-        <v>936.2643379750641</v>
+        <v>936.1843379750594</v>
       </c>
       <c r="J37" t="n">
-        <v>1286.695337807843</v>
+        <v>1286.615337807839</v>
       </c>
       <c r="K37" t="n">
-        <v>1414.582122564384</v>
+        <v>1414.502122564379</v>
       </c>
       <c r="L37" t="n">
-        <v>1428.919800524248</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="M37" t="n">
-        <v>1350.592142045103</v>
+        <v>1350.512142045098</v>
       </c>
       <c r="N37" t="n">
-        <v>1218.844525029492</v>
+        <v>1218.764525029487</v>
       </c>
       <c r="O37" t="n">
-        <v>1009.753228311162</v>
+        <v>1009.673228311158</v>
       </c>
       <c r="P37" t="n">
-        <v>740.2908382296102</v>
+        <v>740.2108382296055</v>
       </c>
       <c r="Q37" t="n">
-        <v>408.5309731532486</v>
+        <v>408.4509731532439</v>
       </c>
       <c r="R37" t="n">
-        <v>51.49391723587462</v>
+        <v>51.41391723586987</v>
       </c>
       <c r="S37" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="T37" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="U37" t="n">
-        <v>44.96000000000474</v>
+        <v>237.0149824743522</v>
       </c>
       <c r="V37" t="n">
-        <v>44.96000000000474</v>
+        <v>237.0149824743522</v>
       </c>
       <c r="W37" t="n">
-        <v>56.24316531901904</v>
+        <v>354.4559007340296</v>
       </c>
       <c r="X37" t="n">
-        <v>152.8239563432126</v>
+        <v>354.4559007340296</v>
       </c>
       <c r="Y37" t="n">
-        <v>209.7832570222448</v>
+        <v>354.4559007340296</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>443.3918839658645</v>
+        <v>444.0238605876112</v>
       </c>
       <c r="C38" t="n">
-        <v>337.8620069527393</v>
+        <v>338.4939835744861</v>
       </c>
       <c r="D38" t="n">
-        <v>271.8628597407698</v>
+        <v>272.4948363625166</v>
       </c>
       <c r="E38" t="n">
-        <v>211.899940945953</v>
+        <v>212.5319175676998</v>
       </c>
       <c r="F38" t="n">
-        <v>151.4053664934158</v>
+        <v>152.0373431151626</v>
       </c>
       <c r="G38" t="n">
-        <v>93.46355092508816</v>
+        <v>94.09552754683496</v>
       </c>
       <c r="H38" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="I38" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="J38" t="n">
-        <v>127.4802050736467</v>
+        <v>553.4018942939372</v>
       </c>
       <c r="K38" t="n">
-        <v>683.8602050737053</v>
+        <v>729.0734691180577</v>
       </c>
       <c r="L38" t="n">
-        <v>1240.240205073764</v>
+        <v>947.0095916306205</v>
       </c>
       <c r="M38" t="n">
-        <v>1796.620205073786</v>
+        <v>1327.159243836194</v>
       </c>
       <c r="N38" t="n">
-        <v>1886.549243836451</v>
+        <v>1882.549243836214</v>
       </c>
       <c r="O38" t="n">
-        <v>2049.691050093778</v>
+        <v>2045.691050093541</v>
       </c>
       <c r="P38" t="n">
-        <v>2248.000000000237</v>
+        <v>2244</v>
       </c>
       <c r="Q38" t="n">
-        <v>2248.000000000237</v>
+        <v>2244</v>
       </c>
       <c r="R38" t="n">
-        <v>2248.000000000265</v>
+        <v>2244.000000000095</v>
       </c>
       <c r="S38" t="n">
-        <v>2128.747295098675</v>
+        <v>2124.747295098505</v>
       </c>
       <c r="T38" t="n">
-        <v>1890.798730234027</v>
+        <v>1886.798730233857</v>
       </c>
       <c r="U38" t="n">
-        <v>1583.61721653841</v>
+        <v>1579.61721653824</v>
       </c>
       <c r="V38" t="n">
-        <v>1295.888909299194</v>
+        <v>1291.888909299024</v>
       </c>
       <c r="W38" t="n">
-        <v>999.5520648739944</v>
+        <v>1000.184041495741</v>
       </c>
       <c r="X38" t="n">
-        <v>749.7724351157442</v>
+        <v>750.404411737491</v>
       </c>
       <c r="Y38" t="n">
-        <v>581.7750283654348</v>
+        <v>582.4070049871815</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>412.67474681134</v>
+        <v>1101.795089801022</v>
       </c>
       <c r="C39" t="n">
-        <v>47.92736050273467</v>
+        <v>1085.532551977265</v>
       </c>
       <c r="D39" t="n">
-        <v>44.96000000000474</v>
+        <v>734.0803429896864</v>
       </c>
       <c r="E39" t="n">
-        <v>44.96000000000474</v>
+        <v>387.9469114524009</v>
       </c>
       <c r="F39" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="G39" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="H39" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="I39" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="J39" t="n">
-        <v>238.7276497036056</v>
+        <v>238.6476497036008</v>
       </c>
       <c r="K39" t="n">
-        <v>547.2388055149702</v>
+        <v>547.1588055149654</v>
       </c>
       <c r="L39" t="n">
-        <v>979.0274996573402</v>
+        <v>978.9474996573354</v>
       </c>
       <c r="M39" t="n">
-        <v>1252.331891400199</v>
+        <v>1252.251891400195</v>
       </c>
       <c r="N39" t="n">
-        <v>1577.791284215315</v>
+        <v>1575.521778846869</v>
       </c>
       <c r="O39" t="n">
-        <v>1992.640074672619</v>
+        <v>1990.370569304173</v>
       </c>
       <c r="P39" t="n">
-        <v>2246.26950536854</v>
+        <v>2244.000000000095</v>
       </c>
       <c r="Q39" t="n">
-        <v>2246.26950536854</v>
+        <v>2244.000000000095</v>
       </c>
       <c r="R39" t="n">
-        <v>1740.276647421216</v>
+        <v>2001.699598411275</v>
       </c>
       <c r="S39" t="n">
-        <v>1631.488397028146</v>
+        <v>1892.911348018205</v>
       </c>
       <c r="T39" t="n">
-        <v>1494.347226554572</v>
+        <v>1834.982721059405</v>
       </c>
       <c r="U39" t="n">
-        <v>1438.628786164065</v>
+        <v>1779.264280668898</v>
       </c>
       <c r="V39" t="n">
-        <v>1019.931142536266</v>
+        <v>1709.051485525948</v>
       </c>
       <c r="W39" t="n">
-        <v>583.1905941425001</v>
+        <v>1272.310937132182</v>
       </c>
       <c r="X39" t="n">
-        <v>507.5716654097855</v>
+        <v>1196.692008399467</v>
       </c>
       <c r="Y39" t="n">
-        <v>452.6308646359124</v>
+        <v>1141.751207625594</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>632.0055633562355</v>
+        <v>580.3631094381268</v>
       </c>
       <c r="C40" t="n">
-        <v>703.5575691746712</v>
+        <v>580.3631094381268</v>
       </c>
       <c r="D40" t="n">
-        <v>703.5575691746712</v>
+        <v>639.2322535631268</v>
       </c>
       <c r="E40" t="n">
-        <v>703.5575691746712</v>
+        <v>702.6111577745398</v>
       </c>
       <c r="F40" t="n">
-        <v>703.5575691746712</v>
+        <v>772.5221303664753</v>
       </c>
       <c r="G40" t="n">
-        <v>703.5575691746712</v>
+        <v>772.5221303664753</v>
       </c>
       <c r="H40" t="n">
-        <v>824.1318976127574</v>
+        <v>893.0964588045614</v>
       </c>
       <c r="I40" t="n">
-        <v>1009.44423949966</v>
+        <v>1078.408800691464</v>
       </c>
       <c r="J40" t="n">
-        <v>1301.033015767707</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="K40" t="n">
-        <v>1428.919800524248</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="L40" t="n">
-        <v>1428.919800524248</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="M40" t="n">
-        <v>1350.592142045103</v>
+        <v>1350.512142045098</v>
       </c>
       <c r="N40" t="n">
-        <v>1218.844525029492</v>
+        <v>1218.764525029487</v>
       </c>
       <c r="O40" t="n">
-        <v>1009.753228311162</v>
+        <v>1009.673228311158</v>
       </c>
       <c r="P40" t="n">
-        <v>740.2908382296102</v>
+        <v>740.2108382296055</v>
       </c>
       <c r="Q40" t="n">
-        <v>408.5309731532486</v>
+        <v>408.4509731532439</v>
       </c>
       <c r="R40" t="n">
-        <v>51.49391723587463</v>
+        <v>51.41391723586989</v>
       </c>
       <c r="S40" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="T40" t="n">
-        <v>181.2325496506129</v>
+        <v>69.45651513911895</v>
       </c>
       <c r="U40" t="n">
-        <v>373.3675321249651</v>
+        <v>261.5914976134712</v>
       </c>
       <c r="V40" t="n">
-        <v>517.7389250109111</v>
+        <v>405.9628904994171</v>
       </c>
       <c r="W40" t="n">
-        <v>517.7389250109111</v>
+        <v>523.4038087590945</v>
       </c>
       <c r="X40" t="n">
-        <v>517.7389250109111</v>
+        <v>523.4038087590945</v>
       </c>
       <c r="Y40" t="n">
-        <v>574.6982256899433</v>
+        <v>580.3631094381268</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>443.3918839658363</v>
+        <v>439.3918839655994</v>
       </c>
       <c r="C41" t="n">
-        <v>337.8620069527111</v>
+        <v>333.8620069524742</v>
       </c>
       <c r="D41" t="n">
-        <v>271.8628597407416</v>
+        <v>267.8628597405047</v>
       </c>
       <c r="E41" t="n">
-        <v>211.8999409459248</v>
+        <v>207.8999409456879</v>
       </c>
       <c r="F41" t="n">
-        <v>151.4053664933876</v>
+        <v>147.4053664931506</v>
       </c>
       <c r="G41" t="n">
-        <v>93.46355092505993</v>
+        <v>94.09552754683496</v>
       </c>
       <c r="H41" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="I41" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="J41" t="n">
-        <v>127.4802050736467</v>
+        <v>127.400205073642</v>
       </c>
       <c r="K41" t="n">
-        <v>683.8602050737053</v>
+        <v>682.790205073642</v>
       </c>
       <c r="L41" t="n">
-        <v>1240.240205073764</v>
+        <v>1238.180205073642</v>
       </c>
       <c r="M41" t="n">
-        <v>1330.169243836429</v>
+        <v>1327.15924383618</v>
       </c>
       <c r="N41" t="n">
-        <v>1886.549243836451</v>
+        <v>1327.15924383618</v>
       </c>
       <c r="O41" t="n">
-        <v>2049.691050093778</v>
+        <v>1490.301050093507</v>
       </c>
       <c r="P41" t="n">
-        <v>2248.000000000237</v>
+        <v>1688.609999999966</v>
       </c>
       <c r="Q41" t="n">
-        <v>2248.000000000237</v>
+        <v>2244</v>
       </c>
       <c r="R41" t="n">
-        <v>2248.000000000237</v>
+        <v>2244</v>
       </c>
       <c r="S41" t="n">
-        <v>2128.747295098647</v>
+        <v>2124.74729509841</v>
       </c>
       <c r="T41" t="n">
-        <v>1890.798730233999</v>
+        <v>1886.798730233762</v>
       </c>
       <c r="U41" t="n">
-        <v>1583.617216538382</v>
+        <v>1579.617216538145</v>
       </c>
       <c r="V41" t="n">
-        <v>1295.888909299166</v>
+        <v>1291.888909298929</v>
       </c>
       <c r="W41" t="n">
-        <v>999.5520648739662</v>
+        <v>995.5520648737293</v>
       </c>
       <c r="X41" t="n">
-        <v>749.772435115716</v>
+        <v>745.7724351154791</v>
       </c>
       <c r="Y41" t="n">
-        <v>581.7750283654066</v>
+        <v>577.7750283651696</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>143.402441841266</v>
+        <v>1186.587481927424</v>
       </c>
       <c r="C42" t="n">
-        <v>127.1399040175091</v>
+        <v>821.8400956188189</v>
       </c>
       <c r="D42" t="n">
-        <v>124.1725435147792</v>
+        <v>470.3878866312404</v>
       </c>
       <c r="E42" t="n">
-        <v>124.1725435147792</v>
+        <v>470.3878866312404</v>
       </c>
       <c r="F42" t="n">
-        <v>124.1725435147792</v>
+        <v>127.3209751788395</v>
       </c>
       <c r="G42" t="n">
-        <v>44.96000000000474</v>
+        <v>127.3209751788395</v>
       </c>
       <c r="H42" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="I42" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="J42" t="n">
-        <v>238.7276497036056</v>
+        <v>236.4581443352184</v>
       </c>
       <c r="K42" t="n">
-        <v>547.2388055149702</v>
+        <v>544.9693001465829</v>
       </c>
       <c r="L42" t="n">
-        <v>979.0274996573402</v>
+        <v>976.7579942889529</v>
       </c>
       <c r="M42" t="n">
-        <v>1252.331891400199</v>
+        <v>1250.062386031812</v>
       </c>
       <c r="N42" t="n">
-        <v>1577.791284215315</v>
+        <v>1575.521778846928</v>
       </c>
       <c r="O42" t="n">
-        <v>1992.640074672619</v>
+        <v>1990.370569304232</v>
       </c>
       <c r="P42" t="n">
-        <v>2246.26950536854</v>
+        <v>2244.000000000153</v>
       </c>
       <c r="Q42" t="n">
-        <v>2246.26950536854</v>
+        <v>2244.000000000153</v>
       </c>
       <c r="R42" t="n">
-        <v>1740.276647421216</v>
+        <v>2086.491990537677</v>
       </c>
       <c r="S42" t="n">
-        <v>1631.488397028146</v>
+        <v>1977.703740144607</v>
       </c>
       <c r="T42" t="n">
-        <v>1225.074921584497</v>
+        <v>1919.775113185807</v>
       </c>
       <c r="U42" t="n">
-        <v>820.871632709142</v>
+        <v>1864.0566727953</v>
       </c>
       <c r="V42" t="n">
-        <v>750.6588375661923</v>
+        <v>1793.843877652351</v>
       </c>
       <c r="W42" t="n">
-        <v>662.4031376572747</v>
+        <v>1705.588177743433</v>
       </c>
       <c r="X42" t="n">
-        <v>586.7842089245599</v>
+        <v>1629.969249010718</v>
       </c>
       <c r="Y42" t="n">
-        <v>183.3585596658384</v>
+        <v>1575.028448236845</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>846.0272726401065</v>
+        <v>749.3664816159082</v>
       </c>
       <c r="C43" t="n">
-        <v>917.5792784585423</v>
+        <v>749.3664816159082</v>
       </c>
       <c r="D43" t="n">
-        <v>976.4484225835423</v>
+        <v>749.3664816159082</v>
       </c>
       <c r="E43" t="n">
-        <v>1039.827326794955</v>
+        <v>812.7453858273212</v>
       </c>
       <c r="F43" t="n">
-        <v>1109.738299386891</v>
+        <v>882.6563584192568</v>
       </c>
       <c r="G43" t="n">
-        <v>1109.738299386891</v>
+        <v>882.6563584192568</v>
       </c>
       <c r="H43" t="n">
-        <v>1230.312627824977</v>
+        <v>882.6563584192568</v>
       </c>
       <c r="I43" t="n">
-        <v>1415.624969711879</v>
+        <v>936.1843379750594</v>
       </c>
       <c r="J43" t="n">
-        <v>1424.505969544658</v>
+        <v>1286.615337807839</v>
       </c>
       <c r="K43" t="n">
-        <v>1424.505969544658</v>
+        <v>1414.502122564379</v>
       </c>
       <c r="L43" t="n">
-        <v>1428.919800524248</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="M43" t="n">
-        <v>1350.592142045103</v>
+        <v>1350.512142045098</v>
       </c>
       <c r="N43" t="n">
-        <v>1218.844525029492</v>
+        <v>1218.764525029487</v>
       </c>
       <c r="O43" t="n">
-        <v>1009.753228311162</v>
+        <v>1009.673228311158</v>
       </c>
       <c r="P43" t="n">
-        <v>740.2908382296102</v>
+        <v>740.2108382296055</v>
       </c>
       <c r="Q43" t="n">
-        <v>408.5309731532486</v>
+        <v>408.4509731532439</v>
       </c>
       <c r="R43" t="n">
-        <v>51.49391723587462</v>
+        <v>51.41391723586989</v>
       </c>
       <c r="S43" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="T43" t="n">
-        <v>181.2325496506129</v>
+        <v>181.1525496506081</v>
       </c>
       <c r="U43" t="n">
-        <v>373.3675321249651</v>
+        <v>373.2875321249604</v>
       </c>
       <c r="V43" t="n">
-        <v>517.7389250109111</v>
+        <v>517.6589250109064</v>
       </c>
       <c r="W43" t="n">
-        <v>635.1798432705885</v>
+        <v>635.0998432705838</v>
       </c>
       <c r="X43" t="n">
-        <v>731.7606342947821</v>
+        <v>635.0998432705838</v>
       </c>
       <c r="Y43" t="n">
-        <v>788.7199349738144</v>
+        <v>692.0591439496161</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>443.3918839658363</v>
+        <v>439.3918839655994</v>
       </c>
       <c r="C44" t="n">
-        <v>337.8620069527111</v>
+        <v>333.8620069524742</v>
       </c>
       <c r="D44" t="n">
-        <v>271.8628597407416</v>
+        <v>267.8628597405047</v>
       </c>
       <c r="E44" t="n">
-        <v>211.8999409459248</v>
+        <v>207.8999409456879</v>
       </c>
       <c r="F44" t="n">
-        <v>151.4053664933876</v>
+        <v>147.4053664931506</v>
       </c>
       <c r="G44" t="n">
-        <v>93.46355092505996</v>
+        <v>94.09552754683497</v>
       </c>
       <c r="H44" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="I44" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="J44" t="n">
-        <v>127.4802050736467</v>
+        <v>127.400205073642</v>
       </c>
       <c r="K44" t="n">
-        <v>683.8602050737053</v>
+        <v>682.790205073642</v>
       </c>
       <c r="L44" t="n">
-        <v>1240.240205073764</v>
+        <v>1238.180205073642</v>
       </c>
       <c r="M44" t="n">
-        <v>1330.169243836436</v>
+        <v>1327.159243836151</v>
       </c>
       <c r="N44" t="n">
-        <v>1886.549243836451</v>
+        <v>1327.159243836151</v>
       </c>
       <c r="O44" t="n">
-        <v>2049.691050093778</v>
+        <v>1490.301050093478</v>
       </c>
       <c r="P44" t="n">
-        <v>2248.000000000237</v>
+        <v>1688.609999999937</v>
       </c>
       <c r="Q44" t="n">
-        <v>2248.000000000237</v>
+        <v>2244</v>
       </c>
       <c r="R44" t="n">
-        <v>2248.000000000237</v>
+        <v>2244</v>
       </c>
       <c r="S44" t="n">
-        <v>2128.747295098647</v>
+        <v>2124.74729509841</v>
       </c>
       <c r="T44" t="n">
-        <v>1890.798730233999</v>
+        <v>1886.798730233762</v>
       </c>
       <c r="U44" t="n">
-        <v>1583.617216538382</v>
+        <v>1579.617216538145</v>
       </c>
       <c r="V44" t="n">
-        <v>1295.888909299166</v>
+        <v>1291.888909298929</v>
       </c>
       <c r="W44" t="n">
-        <v>999.5520648739662</v>
+        <v>995.5520648737293</v>
       </c>
       <c r="X44" t="n">
-        <v>749.772435115716</v>
+        <v>745.7724351154791</v>
       </c>
       <c r="Y44" t="n">
-        <v>581.7750283654066</v>
+        <v>577.7750283651696</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>412.6747468113401</v>
+        <v>1412.179649921003</v>
       </c>
       <c r="C45" t="n">
-        <v>396.4122089875832</v>
+        <v>1047.432263612397</v>
       </c>
       <c r="D45" t="n">
-        <v>44.96000000000474</v>
+        <v>1044.464903109667</v>
       </c>
       <c r="E45" t="n">
-        <v>44.96000000000474</v>
+        <v>1044.464903109667</v>
       </c>
       <c r="F45" t="n">
-        <v>44.96000000000474</v>
+        <v>701.3979916572664</v>
       </c>
       <c r="G45" t="n">
-        <v>44.96000000000474</v>
+        <v>373.1220739637949</v>
       </c>
       <c r="H45" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="I45" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="J45" t="n">
-        <v>238.7276497036056</v>
+        <v>236.4581443350651</v>
       </c>
       <c r="K45" t="n">
-        <v>547.2388055149702</v>
+        <v>544.9693001464296</v>
       </c>
       <c r="L45" t="n">
-        <v>979.0274996573402</v>
+        <v>976.7579942887996</v>
       </c>
       <c r="M45" t="n">
-        <v>1252.331891400199</v>
+        <v>1250.062386031659</v>
       </c>
       <c r="N45" t="n">
-        <v>1577.791284215315</v>
+        <v>1575.521778846774</v>
       </c>
       <c r="O45" t="n">
-        <v>1992.640074672619</v>
+        <v>1990.370569304078</v>
       </c>
       <c r="P45" t="n">
-        <v>2246.26950536854</v>
+        <v>2244</v>
       </c>
       <c r="Q45" t="n">
-        <v>2246.26950536854</v>
+        <v>2244</v>
       </c>
       <c r="R45" t="n">
-        <v>2088.761495906064</v>
+        <v>2086.491990537524</v>
       </c>
       <c r="S45" t="n">
-        <v>1631.488397028146</v>
+        <v>1977.703740144454</v>
       </c>
       <c r="T45" t="n">
-        <v>1573.559770069346</v>
+        <v>1796.882432694537</v>
       </c>
       <c r="U45" t="n">
-        <v>1169.35648119399</v>
+        <v>1741.16399230403</v>
       </c>
       <c r="V45" t="n">
-        <v>750.658837566192</v>
+        <v>1670.95119716108</v>
       </c>
       <c r="W45" t="n">
-        <v>662.4031376572743</v>
+        <v>1582.695497252163</v>
       </c>
       <c r="X45" t="n">
-        <v>586.7842089245596</v>
+        <v>1507.076568519448</v>
       </c>
       <c r="Y45" t="n">
-        <v>531.8434081506865</v>
+        <v>1452.135767745575</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>490.8084503846425</v>
+        <v>635.0998432705838</v>
       </c>
       <c r="C46" t="n">
-        <v>562.3604562030783</v>
+        <v>706.6518490890196</v>
       </c>
       <c r="D46" t="n">
-        <v>621.2296003280784</v>
+        <v>706.6518490890196</v>
       </c>
       <c r="E46" t="n">
-        <v>621.2296003280784</v>
+        <v>706.6518490890196</v>
       </c>
       <c r="F46" t="n">
-        <v>691.1405729200139</v>
+        <v>706.6518490890196</v>
       </c>
       <c r="G46" t="n">
-        <v>790.7166191347681</v>
+        <v>706.6518490890196</v>
       </c>
       <c r="H46" t="n">
-        <v>911.2909475728542</v>
+        <v>827.2261775271057</v>
       </c>
       <c r="I46" t="n">
-        <v>1096.603289459757</v>
+        <v>950.5220159349235</v>
       </c>
       <c r="J46" t="n">
-        <v>1286.695337807843</v>
+        <v>1300.953015767703</v>
       </c>
       <c r="K46" t="n">
-        <v>1414.582122564384</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="L46" t="n">
-        <v>1428.919800524248</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="M46" t="n">
-        <v>1350.592142045103</v>
+        <v>1350.512142045098</v>
       </c>
       <c r="N46" t="n">
-        <v>1218.844525029492</v>
+        <v>1218.764525029487</v>
       </c>
       <c r="O46" t="n">
-        <v>1009.753228311162</v>
+        <v>1009.673228311158</v>
       </c>
       <c r="P46" t="n">
-        <v>740.2908382296102</v>
+        <v>740.2108382296055</v>
       </c>
       <c r="Q46" t="n">
-        <v>408.5309731532486</v>
+        <v>408.4509731532439</v>
       </c>
       <c r="R46" t="n">
-        <v>51.49391723587463</v>
+        <v>51.41391723586987</v>
       </c>
       <c r="S46" t="n">
-        <v>44.96000000000474</v>
+        <v>44.88</v>
       </c>
       <c r="T46" t="n">
-        <v>181.2325496506129</v>
+        <v>181.1525496506081</v>
       </c>
       <c r="U46" t="n">
-        <v>373.3675321249651</v>
+        <v>373.2875321249604</v>
       </c>
       <c r="V46" t="n">
-        <v>373.3675321249651</v>
+        <v>517.6589250109064</v>
       </c>
       <c r="W46" t="n">
-        <v>490.8084503846425</v>
+        <v>635.0998432705838</v>
       </c>
       <c r="X46" t="n">
-        <v>490.8084503846425</v>
+        <v>635.0998432705838</v>
       </c>
       <c r="Y46" t="n">
-        <v>490.8084503846425</v>
+        <v>635.0998432705838</v>
       </c>
     </row>
   </sheetData>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L2" t="n">
-        <v>183.3412755627362</v>
+        <v>308.6565929648241</v>
       </c>
       <c r="M2" t="n">
-        <v>846.2608914614127</v>
+        <v>471.5549969890509</v>
       </c>
       <c r="N2" t="n">
-        <v>778.0826666125488</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>502.5418702571336</v>
+        <v>427.6391621152114</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L5" t="n">
-        <v>309.2909949748743</v>
+        <v>234.2887077235403</v>
       </c>
       <c r="M5" t="n">
-        <v>772.4711016975159</v>
+        <v>471.5549969890509</v>
       </c>
       <c r="N5" t="n">
-        <v>778.0826666125488</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>128.5418702571336</v>
+        <v>128.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8675,25 +8675,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>52.20524429354373</v>
+        <v>250.7139270839917</v>
       </c>
       <c r="L11" t="n">
-        <v>428.8625025125627</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>948.3167457327697</v>
+        <v>300.0226402051314</v>
       </c>
       <c r="N11" t="n">
-        <v>228.3401037984784</v>
+        <v>229.057420381393</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>448.2660248648043</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>471.5539648241206</v>
+        <v>470.5539648241206</v>
       </c>
       <c r="L14" t="n">
-        <v>428.8625025125627</v>
+        <v>427.8625025125627</v>
       </c>
       <c r="M14" t="n">
-        <v>948.3167457327697</v>
+        <v>690.3746745633521</v>
       </c>
       <c r="N14" t="n">
-        <v>402.6623651748134</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -9152,22 +9152,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>471.5539648241206</v>
+        <v>193.7864667798465</v>
       </c>
       <c r="L17" t="n">
-        <v>172.8800273027414</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>948.3167457327697</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N17" t="n">
-        <v>228.3401037984784</v>
+        <v>876.3401037984806</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>447.6879293874174</v>
       </c>
       <c r="Q17" t="n">
         <v>22.18109136266131</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>471.5539648241206</v>
+        <v>470.5539648241206</v>
       </c>
       <c r="L20" t="n">
-        <v>428.8625025125627</v>
+        <v>225.2494494362334</v>
       </c>
       <c r="M20" t="n">
-        <v>948.3167457327697</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N20" t="n">
-        <v>402.6623651748134</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,16 +9626,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>471.5539648241206</v>
+        <v>470.5539648241206</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>427.8625025125627</v>
       </c>
       <c r="M23" t="n">
-        <v>902.5015096216675</v>
+        <v>947.3167457327718</v>
       </c>
       <c r="N23" t="n">
-        <v>877.3401037984784</v>
+        <v>401.7027692152158</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9860,19 +9860,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>472.5539648241206</v>
       </c>
       <c r="L26" t="n">
-        <v>427.6983246726147</v>
+        <v>231.1686413554253</v>
       </c>
       <c r="M26" t="n">
-        <v>949.3167457327697</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N26" t="n">
-        <v>878.3401037984784</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,22 +10097,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
         <v>472.5539648241206</v>
       </c>
       <c r="L29" t="n">
-        <v>119.9340631387233</v>
+        <v>429.8625025125627</v>
       </c>
       <c r="M29" t="n">
-        <v>299.3167457327696</v>
+        <v>694.2938664825442</v>
       </c>
       <c r="N29" t="n">
-        <v>878.3401037984784</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O29" t="n">
-        <v>485.2102967097708</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -10337,16 +10337,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>472.5539648241206</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>429.8625025125627</v>
       </c>
       <c r="M32" t="n">
-        <v>949.3167457327697</v>
+        <v>474.5986030687008</v>
       </c>
       <c r="N32" t="n">
-        <v>712.3674465641809</v>
+        <v>878.3401037984784</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,19 +10571,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>45.0866411295973</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>341.862502512622</v>
+        <v>253.2942842685632</v>
       </c>
       <c r="M35" t="n">
-        <v>299.3167457327696</v>
+        <v>860.3167457327752</v>
       </c>
       <c r="N35" t="n">
-        <v>228.3401037984784</v>
+        <v>789.3401037984838</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>584.1810913626905</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10650,7 +10650,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>227.4647419277884</v>
+        <v>225.2531203434461</v>
       </c>
       <c r="K36" t="n">
         <v>295.8802408630135</v>
@@ -10808,19 +10808,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>384.5539648241797</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>341.8625025126221</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>861.3167457327918</v>
+        <v>683.3062934151671</v>
       </c>
       <c r="N38" t="n">
-        <v>319.1775166900592</v>
+        <v>789.3401037984984</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10899,7 +10899,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N39" t="n">
-        <v>485.4085271713503</v>
+        <v>483.1969055870668</v>
       </c>
       <c r="O39" t="n">
         <v>382.6817988009037</v>
@@ -11048,16 +11048,16 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>384.5539648241797</v>
+        <v>383.5539648241206</v>
       </c>
       <c r="L41" t="n">
-        <v>341.8625025126221</v>
+        <v>340.8625025125627</v>
       </c>
       <c r="M41" t="n">
-        <v>390.1541586243505</v>
+        <v>389.1945626646257</v>
       </c>
       <c r="N41" t="n">
-        <v>790.3401037985004</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>22.18109136266131</v>
+        <v>583.181091362696</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11124,7 +11124,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>227.4647419277884</v>
+        <v>225.2531203435637</v>
       </c>
       <c r="K42" t="n">
         <v>295.8802408630135</v>
@@ -11285,16 +11285,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>384.5539648241797</v>
+        <v>383.5539648241206</v>
       </c>
       <c r="L44" t="n">
-        <v>341.8625025126221</v>
+        <v>340.8625025125627</v>
       </c>
       <c r="M44" t="n">
-        <v>390.1541586243575</v>
+        <v>389.1945626645968</v>
       </c>
       <c r="N44" t="n">
-        <v>790.3401037984934</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>22.18109136266131</v>
+        <v>583.1810913627251</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11361,7 +11361,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>227.4647419277884</v>
+        <v>225.2531203434089</v>
       </c>
       <c r="K45" t="n">
         <v>295.8802408630135</v>
@@ -23241,7 +23241,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3.110775448756385</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23511,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.956056855791758</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -23712,7 +23712,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2.956056855791442</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.956056855791758</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24186,7 +24186,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2.95605685579163</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -25170,13 +25170,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>4.585656855791399</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0.7048568555617862</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -25374,7 +25374,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7048568555340182</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25419,7 +25419,7 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>4.585656855697664</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -25608,10 +25608,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>4.585656855791804</v>
       </c>
       <c r="H41" t="n">
-        <v>0.704856855561971</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25845,10 +25845,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>4.585656855791843</v>
       </c>
       <c r="H44" t="n">
-        <v>0.7048568555619283</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>822253.6046425482</v>
+        <v>822143.7626425482</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1546395.40283379</v>
+        <v>1546285.56083379</v>
       </c>
     </row>
     <row r="4">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2993770.375882942</v>
+        <v>2993643.282539137</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3717912.174074184</v>
+        <v>3717539.94000809</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4442053.972265426</v>
+        <v>4441546.439477043</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5166195.770456665</v>
+        <v>5165552.938945993</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5890337.568647904</v>
+        <v>5889559.438414942</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6614573.921990659</v>
+        <v>6613890.346909212</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7338715.720181898</v>
+        <v>7338032.145100451</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8062857.518373143</v>
+        <v>8062173.943291696</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8778646.201932782</v>
+        <v>8777662.315657252</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9502755.738825751</v>
+        <v>9501594.228334215</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10226865.27571872</v>
+        <v>10225526.14101117</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10950974.81261169</v>
+        <v>10949458.05368813</v>
       </c>
     </row>
   </sheetData>
@@ -26278,40 +26278,40 @@
         <v>1479768.022390799</v>
       </c>
       <c r="E2" t="n">
+        <v>1479477.071563076</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1479491.542393077</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1479491.542393077</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1479491.542393076</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1479491.542393077</v>
+      </c>
+      <c r="J2" t="n">
         <v>1479768.022390799</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1479768.0223908</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1479768.022390799</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1479768.022390799</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1479768.022390799</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1479768.022390798</v>
       </c>
       <c r="K2" t="n">
         <v>1479768.022390798</v>
       </c>
       <c r="L2" t="n">
-        <v>1479768.0223908</v>
+        <v>1479768.022390799</v>
       </c>
       <c r="M2" t="n">
-        <v>1479702.097129098</v>
+        <v>1479339.125905077</v>
       </c>
       <c r="N2" t="n">
-        <v>1479702.0971291</v>
+        <v>1479339.125905085</v>
       </c>
       <c r="O2" t="n">
-        <v>1479702.097129098</v>
+        <v>1479339.125905077</v>
       </c>
       <c r="P2" t="n">
-        <v>1479702.097129098</v>
+        <v>1479339.125905077</v>
       </c>
     </row>
     <row r="3">
@@ -26321,20 +26321,20 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231098</v>
+        <v>232073</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>590173</v>
+      </c>
+      <c r="F3" t="n">
         <v>975</v>
       </c>
-      <c r="E3" t="n">
-        <v>591500</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388800</v>
+        <v>389152</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>85024.00000002085</v>
+        <v>84320</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101187</v>
+        <v>601967.7658514546</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.25402263</v>
+        <v>599959.4017938484</v>
       </c>
       <c r="D4" t="n">
-        <v>598147.4047756542</v>
+        <v>597948.3132650448</v>
       </c>
       <c r="E4" t="n">
-        <v>514005.3727838712</v>
+        <v>513995.2940558941</v>
       </c>
       <c r="F4" t="n">
-        <v>512320.9448683569</v>
+        <v>512067.1546396873</v>
       </c>
       <c r="G4" t="n">
-        <v>510634.1925055168</v>
+        <v>510380.2322060294</v>
       </c>
       <c r="H4" t="n">
-        <v>508945.09902665</v>
+        <v>508690.9684202963</v>
       </c>
       <c r="I4" t="n">
-        <v>507253.6475458712</v>
+        <v>506999.3463948999</v>
       </c>
       <c r="J4" t="n">
-        <v>505486.5503559125</v>
+        <v>505288.8894845269</v>
       </c>
       <c r="K4" t="n">
-        <v>503791.0490533088</v>
+        <v>503593.3881819232</v>
       </c>
       <c r="L4" t="n">
-        <v>502093.1387660968</v>
+        <v>501895.4778947112</v>
       </c>
       <c r="M4" t="n">
-        <v>506566.2673210985</v>
+        <v>506308.9084534674</v>
       </c>
       <c r="N4" t="n">
-        <v>504800.3868513916</v>
+        <v>504542.8135297534</v>
       </c>
       <c r="O4" t="n">
-        <v>503031.9520361905</v>
+        <v>502774.1639503319</v>
       </c>
       <c r="P4" t="n">
-        <v>501260.9436696326</v>
+        <v>501002.9405070185</v>
       </c>
     </row>
     <row r="5">
@@ -26425,28 +26425,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="C5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="D5" t="n">
         <v>58612.2</v>
       </c>
       <c r="E5" t="n">
-        <v>74009.94899999999</v>
+        <v>73927.349</v>
       </c>
       <c r="F5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.149</v>
       </c>
       <c r="G5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.149</v>
       </c>
       <c r="H5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.149</v>
       </c>
       <c r="I5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.149</v>
       </c>
       <c r="J5" t="n">
         <v>74070.74900000001</v>
@@ -26458,16 +26458,16 @@
         <v>74070.74900000001</v>
       </c>
       <c r="M5" t="n">
-        <v>70738.0050000036</v>
+        <v>70677.20499999999</v>
       </c>
       <c r="N5" t="n">
-        <v>70738.0050000036</v>
+        <v>70677.20499999999</v>
       </c>
       <c r="O5" t="n">
-        <v>70738.0050000036</v>
+        <v>70677.20499999999</v>
       </c>
       <c r="P5" t="n">
-        <v>70738.0050000036</v>
+        <v>70677.20499999999</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>587660.4461806804</v>
+        <v>587115.0565393446</v>
       </c>
       <c r="C6" t="n">
-        <v>820767.3683681688</v>
+        <v>821196.4205969503</v>
       </c>
       <c r="D6" t="n">
-        <v>822033.4176151452</v>
+        <v>823207.5091257541</v>
       </c>
       <c r="E6" t="n">
-        <v>300252.700606928</v>
+        <v>301381.4285071819</v>
       </c>
       <c r="F6" t="n">
-        <v>893437.1285224429</v>
+        <v>892500.2387533897</v>
       </c>
       <c r="G6" t="n">
-        <v>895123.8808852823</v>
+        <v>895162.1611870481</v>
       </c>
       <c r="H6" t="n">
-        <v>896812.9743641492</v>
+        <v>896851.4249727803</v>
       </c>
       <c r="I6" t="n">
-        <v>898504.4258449279</v>
+        <v>898543.0469981767</v>
       </c>
       <c r="J6" t="n">
-        <v>511410.7230348857</v>
+        <v>511256.3839062724</v>
       </c>
       <c r="K6" t="n">
-        <v>901906.2243374896</v>
+        <v>902103.8852088752</v>
       </c>
       <c r="L6" t="n">
-        <v>903604.1346247033</v>
+        <v>903801.7954960875</v>
       </c>
       <c r="M6" t="n">
-        <v>817373.8248079747</v>
+        <v>818033.0124516092</v>
       </c>
       <c r="N6" t="n">
-        <v>904163.7052777053</v>
+        <v>904119.1073753316</v>
       </c>
       <c r="O6" t="n">
-        <v>649132.1400929042</v>
+        <v>649087.756954745</v>
       </c>
       <c r="P6" t="n">
-        <v>907703.1484594615</v>
+        <v>907658.9803980583</v>
       </c>
     </row>
   </sheetData>
@@ -26807,16 +26807,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
         <v>103</v>
       </c>
       <c r="E3" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F3" t="n">
         <v>347</v>
@@ -26868,19 +26868,19 @@
         <v>374</v>
       </c>
       <c r="E4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="I4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J4" t="n">
         <v>650</v>
@@ -26892,16 +26892,16 @@
         <v>650</v>
       </c>
       <c r="M4" t="n">
-        <v>562.0000000000592</v>
+        <v>561</v>
       </c>
       <c r="N4" t="n">
-        <v>562.0000000000592</v>
+        <v>561</v>
       </c>
       <c r="O4" t="n">
-        <v>562.0000000000592</v>
+        <v>561</v>
       </c>
       <c r="P4" t="n">
-        <v>562.0000000000592</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -26972,7 +26972,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
@@ -26987,10 +26987,10 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -27024,19 +27024,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>243</v>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>244</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -27085,7 +27085,7 @@
         <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -27100,16 +27100,16 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>187.0000000000521</v>
+        <v>185</v>
       </c>
       <c r="N4" t="n">
         <v>-0</v>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>132.4740095033003</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27521,19 +27521,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>165.6332791194289</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27566,7 +27566,7 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>227.1478262079979</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>341.1837382143316</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27612,16 +27612,16 @@
         <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>171.1020457840527</v>
+        <v>347.9132149025658</v>
       </c>
       <c r="J4" t="n">
-        <v>396.2647849014816</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,13 +27642,13 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9483584875727</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27657,10 +27657,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,10 +27718,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27749,28 +27749,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>214.9783449500132</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,16 +27794,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
-        <v>159.6519859716245</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>391.1776602321171</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>400</v>
+        <v>30.46477465147608</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27831,28 +27831,28 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>396.2647849014815</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
@@ -27882,13 +27882,13 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>357.1328808473952</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V7" t="n">
-        <v>349.5087535872954</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>226.3728098387097</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.1177124465037</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27958,7 +27958,7 @@
         <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
-        <v>398.0465935392085</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27986,16 +27986,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54.54624042207695</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>277.3992913726191</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28034,7 +28034,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>400</v>
+        <v>159.5184388018133</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28043,10 +28043,10 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>400</v>
+        <v>26.19578428848864</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>40.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
@@ -28071,28 +28071,28 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
         <v>244.858135136612</v>
       </c>
       <c r="H10" t="n">
-        <v>329.9591918633881</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J10" t="n">
         <v>396.1372930982029</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,7 +28116,7 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.1365780635112</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
         <v>209.2309599488807</v>
@@ -28128,10 +28128,10 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
+        <v>258.4692435656003</v>
+      </c>
+      <c r="X10" t="n">
         <v>400</v>
-      </c>
-      <c r="X10" t="n">
-        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
         <v>400</v>
@@ -28165,7 +28165,7 @@
         <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>95.37664769425513</v>
+        <v>96.45637576308661</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>163.2515083760331</v>
+        <v>163.5040360142241</v>
       </c>
       <c r="S11" t="n">
         <v>321</v>
@@ -28226,7 +28226,7 @@
         <v>321</v>
       </c>
       <c r="C12" t="n">
-        <v>321</v>
+        <v>141.0298835199132</v>
       </c>
       <c r="D12" t="n">
         <v>321</v>
@@ -28241,10 +28241,10 @@
         <v>321</v>
       </c>
       <c r="H12" t="n">
-        <v>137.8407332208565</v>
+        <v>321</v>
       </c>
       <c r="I12" t="n">
-        <v>191.4287443819146</v>
+        <v>191.5028009856882</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28268,10 +28268,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>77.80484999613995</v>
+        <v>78.07941603387582</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S12" t="n">
         <v>321</v>
@@ -28286,7 +28286,7 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -28359,7 +28359,7 @@
         <v>321</v>
       </c>
       <c r="U13" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="V13" t="n">
         <v>321</v>
@@ -28371,7 +28371,7 @@
         <v>321</v>
       </c>
       <c r="Y13" t="n">
-        <v>321</v>
+        <v>317.8316225849397</v>
       </c>
     </row>
     <row r="14">
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>162.3267652318248</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S14" t="n">
         <v>321</v>
@@ -28460,19 +28460,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
         <v>137.8407332208564</v>
       </c>
       <c r="D15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
@@ -28526,10 +28526,10 @@
         <v>321</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16">
@@ -28599,16 +28599,16 @@
         <v>321</v>
       </c>
       <c r="V16" t="n">
+        <v>321</v>
+      </c>
+      <c r="W16" t="n">
+        <v>321</v>
+      </c>
+      <c r="X16" t="n">
+        <v>321</v>
+      </c>
+      <c r="Y16" t="n">
         <v>315.8198010595348</v>
-      </c>
-      <c r="W16" t="n">
-        <v>321</v>
-      </c>
-      <c r="X16" t="n">
-        <v>321</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>321</v>
       </c>
     </row>
     <row r="17">
@@ -28639,7 +28639,7 @@
         <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>95.37664769425496</v>
+        <v>96.3013908384635</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28700,16 +28700,16 @@
         <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>137.8407332208564</v>
+        <v>321</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
@@ -28745,7 +28745,7 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R18" t="n">
-        <v>321</v>
+        <v>137.8407332208566</v>
       </c>
       <c r="S18" t="n">
         <v>321</v>
@@ -28754,13 +28754,13 @@
         <v>321</v>
       </c>
       <c r="U18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>321</v>
@@ -28803,7 +28803,7 @@
         <v>321</v>
       </c>
       <c r="K19" t="n">
-        <v>315.8198010595346</v>
+        <v>321</v>
       </c>
       <c r="L19" t="n">
         <v>321</v>
@@ -28839,7 +28839,7 @@
         <v>321</v>
       </c>
       <c r="W19" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
       <c r="X19" t="n">
         <v>321</v>
@@ -28876,7 +28876,7 @@
         <v>321</v>
       </c>
       <c r="I20" t="n">
-        <v>95.37664769425513</v>
+        <v>96.3013908384635</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28937,19 +28937,19 @@
         <v>321</v>
       </c>
       <c r="C21" t="n">
+        <v>321</v>
+      </c>
+      <c r="D21" t="n">
+        <v>321</v>
+      </c>
+      <c r="E21" t="n">
+        <v>321</v>
+      </c>
+      <c r="F21" t="n">
+        <v>321</v>
+      </c>
+      <c r="G21" t="n">
         <v>137.8407332208564</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>321</v>
       </c>
       <c r="H21" t="n">
         <v>321</v>
@@ -28991,13 +28991,13 @@
         <v>321</v>
       </c>
       <c r="U21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>321</v>
@@ -29067,7 +29067,7 @@
         <v>321</v>
       </c>
       <c r="T22" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
       <c r="U22" t="n">
         <v>321</v>
@@ -29079,7 +29079,7 @@
         <v>321</v>
       </c>
       <c r="X22" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
       <c r="Y22" t="n">
         <v>321</v>
@@ -29113,7 +29113,7 @@
         <v>321</v>
       </c>
       <c r="I23" t="n">
-        <v>95.37664769425513</v>
+        <v>96.3013908384635</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29174,10 +29174,10 @@
         <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>137.8407332208564</v>
+        <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -29219,10 +29219,10 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>321</v>
+        <v>137.8407332208561</v>
       </c>
       <c r="T24" t="n">
         <v>321</v>
@@ -29277,7 +29277,7 @@
         <v>321</v>
       </c>
       <c r="K25" t="n">
-        <v>321</v>
+        <v>315.8198010595346</v>
       </c>
       <c r="L25" t="n">
         <v>321</v>
@@ -29316,7 +29316,7 @@
         <v>321</v>
       </c>
       <c r="X25" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
       <c r="Y25" t="n">
         <v>321</v>
@@ -29347,7 +29347,7 @@
         <v>321</v>
       </c>
       <c r="H26" t="n">
-        <v>316.1944568557916</v>
+        <v>316.1944568557914</v>
       </c>
       <c r="I26" t="n">
         <v>96.3013908384635</v>
@@ -29408,10 +29408,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>137.8407332208565</v>
       </c>
       <c r="C27" t="n">
-        <v>137.8407332208565</v>
+        <v>321</v>
       </c>
       <c r="D27" t="n">
         <v>321</v>
@@ -29465,19 +29465,19 @@
         <v>321</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28">
@@ -29566,7 +29566,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>321</v>
+        <v>316.1944568557915</v>
       </c>
       <c r="C29" t="n">
         <v>321</v>
@@ -29584,7 +29584,7 @@
         <v>321</v>
       </c>
       <c r="H29" t="n">
-        <v>316.1944568557916</v>
+        <v>321</v>
       </c>
       <c r="I29" t="n">
         <v>96.3013908384635</v>
@@ -29645,13 +29645,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E30" t="n">
         <v>321</v>
@@ -29705,16 +29705,16 @@
         <v>321</v>
       </c>
       <c r="V30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>137.8407332208566</v>
+        <v>137.8407332208565</v>
       </c>
     </row>
     <row r="31">
@@ -29781,7 +29781,7 @@
         <v>321</v>
       </c>
       <c r="U31" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="V31" t="n">
         <v>321</v>
@@ -29793,7 +29793,7 @@
         <v>321</v>
       </c>
       <c r="Y31" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32">
@@ -29824,7 +29824,7 @@
         <v>321</v>
       </c>
       <c r="I32" t="n">
-        <v>91.49584769425496</v>
+        <v>91.49584769425513</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29882,16 +29882,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>321</v>
@@ -29945,13 +29945,13 @@
         <v>321</v>
       </c>
       <c r="W33" t="n">
-        <v>137.8407332208565</v>
+        <v>321</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>137.8407332208566</v>
       </c>
     </row>
     <row r="34">
@@ -30018,7 +30018,7 @@
         <v>321</v>
       </c>
       <c r="U34" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="V34" t="n">
         <v>321</v>
@@ -30030,7 +30030,7 @@
         <v>321</v>
       </c>
       <c r="Y34" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
     </row>
     <row r="35">
@@ -30122,10 +30122,10 @@
         <v>345</v>
       </c>
       <c r="C36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -30137,7 +30137,7 @@
         <v>324.9931585165368</v>
       </c>
       <c r="H36" t="n">
-        <v>238.8475747043197</v>
+        <v>241.0151850191337</v>
       </c>
       <c r="I36" t="n">
         <v>191.4287443819146</v>
@@ -30167,13 +30167,13 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="S36" t="n">
         <v>345</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="U36" t="n">
         <v>345</v>
@@ -30198,7 +30198,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>345</v>
+        <v>299.3670732353178</v>
       </c>
       <c r="C37" t="n">
         <v>345</v>
@@ -30213,7 +30213,7 @@
         <v>345</v>
       </c>
       <c r="G37" t="n">
-        <v>345</v>
+        <v>244.418135136612</v>
       </c>
       <c r="H37" t="n">
         <v>345</v>
@@ -30255,19 +30255,19 @@
         <v>207.3509599488807</v>
       </c>
       <c r="U37" t="n">
-        <v>150.9242601269169</v>
+        <v>345</v>
       </c>
       <c r="V37" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>237.7699465245827</v>
+        <v>345</v>
       </c>
       <c r="X37" t="n">
-        <v>345</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y37" t="n">
-        <v>345</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="38">
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>163.2515083760617</v>
+        <v>163.2515083761273</v>
       </c>
       <c r="S38" t="n">
         <v>345</v>
@@ -30359,16 +30359,16 @@
         <v>345</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="D39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>324.9931585165368</v>
@@ -30404,19 +30404,19 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>261.0555317949189</v>
       </c>
       <c r="S39" t="n">
         <v>345</v>
       </c>
       <c r="T39" t="n">
-        <v>266.5795819203735</v>
+        <v>345</v>
       </c>
       <c r="U39" t="n">
         <v>345</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -30435,19 +30435,19 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C40" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D40" t="n">
         <v>345</v>
       </c>
-      <c r="C40" t="n">
+      <c r="E40" t="n">
         <v>345</v>
       </c>
-      <c r="D40" t="n">
-        <v>285.5362180555555</v>
-      </c>
-      <c r="E40" t="n">
-        <v>280.9809048369565</v>
-      </c>
       <c r="F40" t="n">
-        <v>274.3828559677419</v>
+        <v>345</v>
       </c>
       <c r="G40" t="n">
         <v>244.418135136612</v>
@@ -30459,10 +30459,10 @@
         <v>345</v>
       </c>
       <c r="J40" t="n">
-        <v>285.5634105406751</v>
+        <v>345</v>
       </c>
       <c r="K40" t="n">
-        <v>345</v>
+        <v>215.821429538848</v>
       </c>
       <c r="L40" t="n">
         <v>330.5174970102382</v>
@@ -30489,7 +30489,7 @@
         <v>345</v>
       </c>
       <c r="T40" t="n">
-        <v>345</v>
+        <v>232.1757227156675</v>
       </c>
       <c r="U40" t="n">
         <v>345</v>
@@ -30498,7 +30498,7 @@
         <v>345</v>
       </c>
       <c r="W40" t="n">
-        <v>226.3728098387097</v>
+        <v>345</v>
       </c>
       <c r="X40" t="n">
         <v>247.4436454301076</v>
@@ -30593,25 +30593,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>246.57274043691</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H42" t="n">
-        <v>324.959653224157</v>
+        <v>243.3430877971059</v>
       </c>
       <c r="I42" t="n">
         <v>191.4287443819146</v>
@@ -30641,16 +30641,16 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="S42" t="n">
         <v>345</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="V42" t="n">
         <v>345</v>
@@ -30662,7 +30662,7 @@
         <v>345</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
     </row>
     <row r="43">
@@ -30675,10 +30675,10 @@
         <v>345</v>
       </c>
       <c r="C43" t="n">
-        <v>345</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D43" t="n">
-        <v>345</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E43" t="n">
         <v>345</v>
@@ -30690,19 +30690,19 @@
         <v>244.418135136612</v>
       </c>
       <c r="H43" t="n">
+        <v>223.2077490524383</v>
+      </c>
+      <c r="I43" t="n">
+        <v>211.8844824938384</v>
+      </c>
+      <c r="J43" t="n">
         <v>345</v>
       </c>
-      <c r="I43" t="n">
+      <c r="K43" t="n">
         <v>345</v>
       </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>215.821429538848</v>
-      </c>
       <c r="L43" t="n">
-        <v>334.9759121411366</v>
+        <v>345</v>
       </c>
       <c r="M43" t="n">
         <v>345</v>
@@ -30738,7 +30738,7 @@
         <v>345</v>
       </c>
       <c r="X43" t="n">
-        <v>345</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y43" t="n">
         <v>345</v>
@@ -30830,25 +30830,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>266.5795819203736</v>
+        <v>345</v>
       </c>
       <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
         <v>345</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>324.9931585165368</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>324.959653224157</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>191.4287443819146</v>
@@ -30881,16 +30881,16 @@
         <v>345</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="T45" t="n">
+        <v>223.3362463137944</v>
+      </c>
+      <c r="U45" t="n">
         <v>345</v>
       </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="W45" t="n">
         <v>345</v>
@@ -30915,31 +30915,31 @@
         <v>345</v>
       </c>
       <c r="D46" t="n">
-        <v>345</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E46" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F46" t="n">
-        <v>345</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G46" t="n">
-        <v>345</v>
+        <v>244.418135136612</v>
       </c>
       <c r="H46" t="n">
         <v>345</v>
       </c>
       <c r="I46" t="n">
+        <v>282.3570671928437</v>
+      </c>
+      <c r="J46" t="n">
         <v>345</v>
-      </c>
-      <c r="J46" t="n">
-        <v>183.0414631467749</v>
       </c>
       <c r="K46" t="n">
         <v>345</v>
       </c>
       <c r="L46" t="n">
-        <v>345</v>
+        <v>330.5174970102382</v>
       </c>
       <c r="M46" t="n">
         <v>345</v>
@@ -30969,7 +30969,7 @@
         <v>345</v>
       </c>
       <c r="V46" t="n">
-        <v>199.1703102162162</v>
+        <v>345</v>
       </c>
       <c r="W46" t="n">
         <v>345</v>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I5" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J5" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K5" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M5" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N5" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O5" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P5" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R5" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S5" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I6" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J6" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K6" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L6" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M6" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O6" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P6" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R6" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S6" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I7" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J7" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K7" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L7" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M7" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O7" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P7" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R7" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S7" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31802,49 +31802,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.394974874371858</v>
+        <v>1.390954773869346</v>
       </c>
       <c r="H11" t="n">
-        <v>14.2862864321608</v>
+        <v>14.24511557788944</v>
       </c>
       <c r="I11" t="n">
-        <v>53.77976884422112</v>
+        <v>53.624783919598</v>
       </c>
       <c r="J11" t="n">
-        <v>118.3967487437186</v>
+        <v>118.0555477386935</v>
       </c>
       <c r="K11" t="n">
-        <v>177.4460351758794</v>
+        <v>176.9346633165829</v>
       </c>
       <c r="L11" t="n">
-        <v>220.1374974874372</v>
+        <v>219.5030954773869</v>
       </c>
       <c r="M11" t="n">
-        <v>244.9453819095477</v>
+        <v>244.2394874371859</v>
       </c>
       <c r="N11" t="n">
-        <v>248.9088542713568</v>
+        <v>248.1915376884422</v>
       </c>
       <c r="O11" t="n">
-        <v>235.0375728643216</v>
+        <v>234.3602311557789</v>
       </c>
       <c r="P11" t="n">
-        <v>200.5991306532663</v>
+        <v>200.0210351758794</v>
       </c>
       <c r="Q11" t="n">
-        <v>150.6415929648241</v>
+        <v>150.2074673366834</v>
       </c>
       <c r="R11" t="n">
-        <v>87.62709045226131</v>
+        <v>87.37456281407036</v>
       </c>
       <c r="S11" t="n">
-        <v>31.78798994974875</v>
+        <v>31.69638190954775</v>
       </c>
       <c r="T11" t="n">
-        <v>6.106502512562813</v>
+        <v>6.088904522613064</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1115979899497486</v>
+        <v>0.1112763819095476</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31881,49 +31881,49 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7463773584905661</v>
+        <v>0.7442264150943396</v>
       </c>
       <c r="H12" t="n">
-        <v>7.208433962264152</v>
+        <v>7.187660377358492</v>
       </c>
       <c r="I12" t="n">
-        <v>25.69764150943397</v>
+        <v>25.62358490566038</v>
       </c>
       <c r="J12" t="n">
-        <v>70.5162924528302</v>
+        <v>70.31307547169813</v>
       </c>
       <c r="K12" t="n">
-        <v>120.5235754716981</v>
+        <v>120.1762452830189</v>
       </c>
       <c r="L12" t="n">
-        <v>162.058820754717</v>
+        <v>161.5917924528302</v>
       </c>
       <c r="M12" t="n">
-        <v>189.115</v>
+        <v>188.57</v>
       </c>
       <c r="N12" t="n">
-        <v>194.1203113207547</v>
+        <v>193.5608867924528</v>
       </c>
       <c r="O12" t="n">
-        <v>177.5821603773585</v>
+        <v>177.0703962264151</v>
       </c>
       <c r="P12" t="n">
-        <v>142.5253396226415</v>
+        <v>142.1146037735849</v>
       </c>
       <c r="Q12" t="n">
-        <v>95.27441509433963</v>
+        <v>94.99984905660378</v>
       </c>
       <c r="R12" t="n">
-        <v>46.34086792452832</v>
+        <v>46.207320754717</v>
       </c>
       <c r="S12" t="n">
-        <v>13.86363207547169</v>
+        <v>13.82367924528301</v>
       </c>
       <c r="T12" t="n">
-        <v>3.008424528301886</v>
+        <v>2.999754716981131</v>
       </c>
       <c r="U12" t="n">
-        <v>0.04910377358490568</v>
+        <v>0.04896226415094342</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31960,49 +31960,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6257377049180327</v>
+        <v>0.6239344262295081</v>
       </c>
       <c r="H13" t="n">
-        <v>5.563377049180331</v>
+        <v>5.547344262295085</v>
       </c>
       <c r="I13" t="n">
-        <v>18.8176393442623</v>
+        <v>18.76340983606558</v>
       </c>
       <c r="J13" t="n">
-        <v>44.23965573770491</v>
+        <v>44.11216393442622</v>
       </c>
       <c r="K13" t="n">
-        <v>72.69934426229506</v>
+        <v>72.48983606557374</v>
       </c>
       <c r="L13" t="n">
-        <v>93.03013114754098</v>
+        <v>92.76203278688526</v>
       </c>
       <c r="M13" t="n">
-        <v>98.0872295081967</v>
+        <v>97.80455737704916</v>
       </c>
       <c r="N13" t="n">
-        <v>95.75493442622957</v>
+        <v>95.47898360655743</v>
       </c>
       <c r="O13" t="n">
-        <v>88.44518032786888</v>
+        <v>88.19029508196724</v>
       </c>
       <c r="P13" t="n">
-        <v>75.68013114754095</v>
+        <v>75.4620327868852</v>
       </c>
       <c r="Q13" t="n">
-        <v>52.397</v>
+        <v>52.246</v>
       </c>
       <c r="R13" t="n">
-        <v>28.13544262295081</v>
+        <v>28.0543606557377</v>
       </c>
       <c r="S13" t="n">
-        <v>10.90490163934426</v>
+        <v>10.87347540983606</v>
       </c>
       <c r="T13" t="n">
-        <v>2.673606557377048</v>
+        <v>2.665901639344261</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03413114754098364</v>
+        <v>0.03403278688524593</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -34743,16 +34743,16 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K2" t="n">
-        <v>52.1599296482412</v>
+        <v>374</v>
       </c>
       <c r="L2" t="n">
-        <v>248.0502805878618</v>
+        <v>374</v>
       </c>
       <c r="M2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>374</v>
@@ -34761,10 +34761,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>374</v>
+        <v>299.5314174862185</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K3" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M3" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O3" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P3" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>55.64752015877615</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34892,22 +34892,22 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>155.1400615846995</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8642181606765</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>176.8653986267098</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,10 +34928,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -34943,10 +34943,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34980,16 +34980,16 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>374</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>373.9999999999999</v>
+        <v>299.6321147587162</v>
       </c>
       <c r="M5" t="n">
-        <v>300.2102102361031</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>374</v>
@@ -34998,7 +34998,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K6" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L6" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M6" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O6" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P6" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35117,34 +35117,34 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I7" t="n">
-        <v>228.8979542159473</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>132.8490622644307</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L7" t="n">
-        <v>3.798404629106074</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,16 +35165,16 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.83199570698065</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T7" t="n">
-        <v>190.7613351330866</v>
+        <v>147.9019208985145</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>150.3384433710791</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -35357,28 +35357,28 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>102.8394428109498</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I10" t="n">
-        <v>228.952183724144</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>374</v>
       </c>
       <c r="K10" t="n">
-        <v>133.058570461152</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>4.06650298976183</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -35414,10 +35414,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>32.09643372689065</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
         <v>112.5346471505376</v>
@@ -35454,28 +35454,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>83.35374249862829</v>
+        <v>513.3172780797598</v>
       </c>
       <c r="K11" t="n">
-        <v>229.6512794694231</v>
+        <v>427.6485904005747</v>
       </c>
       <c r="L11" t="n">
-        <v>649</v>
+        <v>219.503095477387</v>
       </c>
       <c r="M11" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>164.7897032902292</v>
+        <v>164.1123615816865</v>
       </c>
       <c r="P11" t="n">
-        <v>200.3120706125849</v>
+        <v>648.0000000000023</v>
       </c>
       <c r="Q11" t="n">
-        <v>593.6709819069124</v>
+        <v>593.2368562787717</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35533,25 +35533,25 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>195.7248986905059</v>
+        <v>195.5216817093738</v>
       </c>
       <c r="K12" t="n">
-        <v>311.6274301124894</v>
+        <v>311.2800999238102</v>
       </c>
       <c r="L12" t="n">
-        <v>436.150196103404</v>
+        <v>435.6831678015172</v>
       </c>
       <c r="M12" t="n">
-        <v>276.0650421645042</v>
+        <v>275.5200421645043</v>
       </c>
       <c r="N12" t="n">
-        <v>328.7468614294096</v>
+        <v>328.1874369011077</v>
       </c>
       <c r="O12" t="n">
-        <v>419.0391822801049</v>
+        <v>418.5274181291614</v>
       </c>
       <c r="P12" t="n">
-        <v>256.1913441372947</v>
+        <v>255.7806082882381</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -35603,19 +35603,19 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G13" t="n">
-        <v>76.58186486338801</v>
+        <v>76.58006158469948</v>
       </c>
       <c r="H13" t="n">
-        <v>97.79225094756171</v>
+        <v>97.77621816067648</v>
       </c>
       <c r="I13" t="n">
-        <v>163.184183724144</v>
+        <v>163.1299542159473</v>
       </c>
       <c r="J13" t="n">
-        <v>329.9707069017971</v>
+        <v>329.8432150985184</v>
       </c>
       <c r="K13" t="n">
-        <v>105.178570461152</v>
+        <v>104.9690622644307</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35642,10 +35642,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>113.6490400511193</v>
+        <v>113.6413351330866</v>
       </c>
       <c r="U13" t="n">
-        <v>164.8955409326178</v>
+        <v>170.0756415124273</v>
       </c>
       <c r="V13" t="n">
         <v>121.8296897837838</v>
@@ -35657,7 +35657,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y13" t="n">
-        <v>33.53464715053764</v>
+        <v>30.36626973547734</v>
       </c>
     </row>
     <row r="14">
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K14" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="L14" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="M14" t="n">
-        <v>649</v>
+        <v>391.0579288305826</v>
       </c>
       <c r="N14" t="n">
-        <v>174.322261376335</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>164.7897032902292</v>
@@ -35885,7 +35885,7 @@
         <v>170.0757398730831</v>
       </c>
       <c r="V16" t="n">
-        <v>116.6494908433185</v>
+        <v>121.8296897837838</v>
       </c>
       <c r="W16" t="n">
         <v>94.62719016129032</v>
@@ -35894,7 +35894,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y16" t="n">
-        <v>33.53464715053764</v>
+        <v>28.35444821007238</v>
       </c>
     </row>
     <row r="17">
@@ -35931,22 +35931,22 @@
         <v>513.658479084785</v>
       </c>
       <c r="K17" t="n">
-        <v>649</v>
+        <v>371.2325019557259</v>
       </c>
       <c r="L17" t="n">
-        <v>393.0175247901786</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M17" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>648.0000000000023</v>
       </c>
       <c r="O17" t="n">
         <v>164.7897032902292</v>
       </c>
       <c r="P17" t="n">
-        <v>200.3120706125849</v>
+        <v>648.0000000000023</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -36089,7 +36089,7 @@
         <v>329.9707069017971</v>
       </c>
       <c r="K19" t="n">
-        <v>99.99837152068662</v>
+        <v>105.178570461152</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -36125,7 +36125,7 @@
         <v>121.8296897837838</v>
       </c>
       <c r="W19" t="n">
-        <v>94.62719016129032</v>
+        <v>89.44699122082511</v>
       </c>
       <c r="X19" t="n">
         <v>73.55635456989245</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K20" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="L20" t="n">
-        <v>649</v>
+        <v>445.3869469236706</v>
       </c>
       <c r="M20" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>174.322261376335</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>164.7897032902292</v>
@@ -36186,7 +36186,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>113.6490400511193</v>
+        <v>108.4688411106541</v>
       </c>
       <c r="U22" t="n">
         <v>170.0757398730831</v>
@@ -36365,7 +36365,7 @@
         <v>94.62719016129032</v>
       </c>
       <c r="X22" t="n">
-        <v>68.37615562942723</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y22" t="n">
         <v>33.53464715053764</v>
@@ -36405,16 +36405,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K23" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="L23" t="n">
-        <v>220.1374974874373</v>
+        <v>648</v>
       </c>
       <c r="M23" t="n">
-        <v>603.1847638888979</v>
+        <v>648.0000000000022</v>
       </c>
       <c r="N23" t="n">
-        <v>649</v>
+        <v>173.3626654167373</v>
       </c>
       <c r="O23" t="n">
         <v>164.7897032902292</v>
@@ -36563,7 +36563,7 @@
         <v>329.9707069017971</v>
       </c>
       <c r="K25" t="n">
-        <v>105.178570461152</v>
+        <v>99.99837152068662</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36602,7 +36602,7 @@
         <v>94.62719016129032</v>
       </c>
       <c r="X25" t="n">
-        <v>68.37615562942723</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y25" t="n">
         <v>33.53464715053764</v>
@@ -36639,19 +36639,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K26" t="n">
-        <v>177.4460351758794</v>
+        <v>650</v>
       </c>
       <c r="L26" t="n">
-        <v>647.8358221600519</v>
+        <v>451.3061388428625</v>
       </c>
       <c r="M26" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>164.7897032902292</v>
@@ -36660,7 +36660,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36876,22 +36876,22 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K29" t="n">
         <v>650</v>
       </c>
       <c r="L29" t="n">
-        <v>340.0715606261606</v>
+        <v>650</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>394.9771207497746</v>
       </c>
       <c r="N29" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>650</v>
+        <v>164.7897032902292</v>
       </c>
       <c r="P29" t="n">
         <v>200.3120706125849</v>
@@ -37067,7 +37067,7 @@
         <v>113.6490400511193</v>
       </c>
       <c r="U31" t="n">
-        <v>170.0757398730831</v>
+        <v>164.8955409326177</v>
       </c>
       <c r="V31" t="n">
         <v>121.8296897837838</v>
@@ -37079,7 +37079,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y31" t="n">
-        <v>28.35444821007238</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="32">
@@ -37116,16 +37116,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K32" t="n">
-        <v>177.4460351758794</v>
+        <v>650</v>
       </c>
       <c r="L32" t="n">
-        <v>220.1374974874373</v>
+        <v>650</v>
       </c>
       <c r="M32" t="n">
+        <v>175.2818573359312</v>
+      </c>
+      <c r="N32" t="n">
         <v>650</v>
-      </c>
-      <c r="N32" t="n">
-        <v>484.0273427657024</v>
       </c>
       <c r="O32" t="n">
         <v>164.7897032902292</v>
@@ -37134,7 +37134,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q32" t="n">
-        <v>593.6709819069124</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37304,7 +37304,7 @@
         <v>113.6490400511193</v>
       </c>
       <c r="U34" t="n">
-        <v>164.8955409326177</v>
+        <v>170.0757398730831</v>
       </c>
       <c r="V34" t="n">
         <v>121.8296897837838</v>
@@ -37316,7 +37316,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y34" t="n">
-        <v>33.53464715053764</v>
+        <v>28.35444821007238</v>
       </c>
     </row>
     <row r="35">
@@ -37350,19 +37350,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K35" t="n">
-        <v>222.5326763054767</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L35" t="n">
-        <v>562.0000000000592</v>
+        <v>473.4317817560004</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>561.0000000000056</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>561.0000000000056</v>
       </c>
       <c r="O35" t="n">
         <v>164.7897032902292</v>
@@ -37371,7 +37371,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q35" t="n">
-        <v>562.0000000000292</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37429,7 +37429,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>195.7248986905059</v>
+        <v>193.5132771061636</v>
       </c>
       <c r="K36" t="n">
         <v>311.6274301124894</v>
@@ -37484,7 +37484,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>57.88619966292134</v>
+        <v>12.25327289823913</v>
       </c>
       <c r="C37" t="n">
         <v>72.27475335195533</v>
@@ -37499,7 +37499,7 @@
         <v>70.61714403225807</v>
       </c>
       <c r="G37" t="n">
-        <v>100.581864863388</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>121.7922509475617</v>
@@ -37541,19 +37541,19 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>194.0757398730831</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>11.39713668587303</v>
+        <v>118.6271901612903</v>
       </c>
       <c r="X37" t="n">
-        <v>97.55635456989245</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>57.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -37587,19 +37587,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K38" t="n">
-        <v>562.0000000000591</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L38" t="n">
-        <v>562.0000000000593</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M38" t="n">
-        <v>562.0000000000222</v>
+        <v>383.9895476823976</v>
       </c>
       <c r="N38" t="n">
-        <v>90.83741289158077</v>
+        <v>561.0000000000201</v>
       </c>
       <c r="O38" t="n">
         <v>164.7897032902292</v>
@@ -37611,7 +37611,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.847912702521291e-11</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -37678,7 +37678,7 @@
         <v>276.0650421645042</v>
       </c>
       <c r="N39" t="n">
-        <v>328.7468614294096</v>
+        <v>326.5352398451261</v>
       </c>
       <c r="O39" t="n">
         <v>419.0391822801049</v>
@@ -37721,19 +37721,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>57.88619966292134</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>72.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>59.46378194444452</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>64.01909516304346</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>70.61714403225807</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -37745,10 +37745,10 @@
         <v>187.184183724144</v>
       </c>
       <c r="J40" t="n">
-        <v>294.5341174424722</v>
+        <v>353.9707069017971</v>
       </c>
       <c r="K40" t="n">
-        <v>129.178570461152</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>137.6490400511193</v>
+        <v>24.82476276678682</v>
       </c>
       <c r="U40" t="n">
         <v>194.0757398730831</v>
@@ -37784,7 +37784,7 @@
         <v>145.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>118.6271901612903</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -37827,16 +37827,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K41" t="n">
-        <v>562.0000000000591</v>
+        <v>561</v>
       </c>
       <c r="L41" t="n">
-        <v>562.0000000000593</v>
+        <v>561</v>
       </c>
       <c r="M41" t="n">
-        <v>90.837412891581</v>
+        <v>89.87781693185615</v>
       </c>
       <c r="N41" t="n">
-        <v>562.0000000000221</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>164.7897032902292</v>
@@ -37845,7 +37845,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>561.0000000000347</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37903,7 +37903,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>195.7248986905059</v>
+        <v>193.5132771062812</v>
       </c>
       <c r="K42" t="n">
         <v>311.6274301124894</v>
@@ -37961,10 +37961,10 @@
         <v>57.88619966292134</v>
       </c>
       <c r="C43" t="n">
-        <v>72.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>59.46378194444452</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>64.01909516304346</v>
@@ -37976,19 +37976,19 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>121.7922509475617</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>187.184183724144</v>
+        <v>54.06866621798245</v>
       </c>
       <c r="J43" t="n">
-        <v>8.970706901797143</v>
+        <v>353.9707069017971</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>129.178570461152</v>
       </c>
       <c r="L43" t="n">
-        <v>4.458415130898405</v>
+        <v>14.48250298976183</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -38024,7 +38024,7 @@
         <v>118.6271901612903</v>
       </c>
       <c r="X43" t="n">
-        <v>97.55635456989245</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
         <v>57.53464715053764</v>
@@ -38064,16 +38064,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K44" t="n">
-        <v>562.0000000000591</v>
+        <v>561</v>
       </c>
       <c r="L44" t="n">
-        <v>562.0000000000593</v>
+        <v>561</v>
       </c>
       <c r="M44" t="n">
-        <v>90.83741289158789</v>
+        <v>89.87781693182721</v>
       </c>
       <c r="N44" t="n">
-        <v>562.0000000000149</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>164.7897032902292</v>
@@ -38082,7 +38082,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>561.0000000000638</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38140,7 +38140,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>195.7248986905059</v>
+        <v>193.5132771061264</v>
       </c>
       <c r="K45" t="n">
         <v>311.6274301124894</v>
@@ -38201,31 +38201,31 @@
         <v>72.27475335195533</v>
       </c>
       <c r="D46" t="n">
-        <v>59.46378194444452</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>70.61714403225807</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>100.581864863388</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>121.7922509475617</v>
       </c>
       <c r="I46" t="n">
-        <v>187.184183724144</v>
+        <v>124.5412509169877</v>
       </c>
       <c r="J46" t="n">
-        <v>192.012170048572</v>
+        <v>353.9707069017971</v>
       </c>
       <c r="K46" t="n">
         <v>129.178570461152</v>
       </c>
       <c r="L46" t="n">
-        <v>14.48250298976183</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -38255,7 +38255,7 @@
         <v>194.0757398730831</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>145.8296897837838</v>
       </c>
       <c r="W46" t="n">
         <v>118.6271901612903</v>
